--- a/example_datasets/planets-info/planets_data_proc.xlsx
+++ b/example_datasets/planets-info/planets_data_proc.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evgen\Desktop\Handbook_Data-Science\example_datasets\planets-info\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61C3774-CCC2-4563-959F-CAE4537D69B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$AH$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$AI$9</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
   <si>
     <t>planetOrder</t>
   </si>
@@ -119,6 +125,9 @@
   </si>
   <si>
     <t>magnetic_field_strength_uT</t>
+  </si>
+  <si>
+    <t>solar_constant * magnetic_field_strength</t>
   </si>
   <si>
     <t>Mercury</t>
@@ -304,11 +313,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0"/>
-  </numFmts>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,18 +338,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADD8E6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -377,7 +377,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -385,28 +385,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -444,7 +471,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -478,6 +505,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -512,9 +540,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -687,8 +716,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AI999"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
@@ -725,9 +754,10 @@
     <col min="32" max="32" width="16.7109375" customWidth="1"/>
     <col min="33" max="33" width="19.7109375" customWidth="1"/>
     <col min="34" max="34" width="26.7109375" customWidth="1"/>
+    <col min="35" max="35" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -830,31 +860,34 @@
       <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI1" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="3">
         <v>4879</v>
       </c>
       <c r="H2">
-        <v>3.3E+23</v>
+        <v>3.3000000000000003E+23</v>
       </c>
       <c r="I2" s="3">
         <v>57900000</v>
@@ -881,22 +914,22 @@
         <v>167</v>
       </c>
       <c r="Q2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T2">
         <v>4.25</v>
       </c>
       <c r="U2">
-        <v>0.034</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="V2">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="W2">
         <v>3.7</v>
@@ -908,7 +941,7 @@
         <v>5.43</v>
       </c>
       <c r="Z2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA2">
         <v>60830000000</v>
@@ -934,31 +967,35 @@
       <c r="AH2">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI2">
+        <f t="shared" ref="AI2:AI65" si="0">SUM(AG2, AH2)</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3">
         <v>12104</v>
       </c>
       <c r="H3">
-        <v>4.87E+24</v>
+        <v>4.8699999999999996E+24</v>
       </c>
       <c r="I3" s="3">
         <v>108200000</v>
@@ -985,13 +1022,13 @@
         <v>464</v>
       </c>
       <c r="Q3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T3">
         <v>10.36</v>
@@ -1003,7 +1040,7 @@
         <v>0.75</v>
       </c>
       <c r="W3">
-        <v>8.869999999999999</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="X3">
         <v>243</v>
@@ -1012,19 +1049,19 @@
         <v>5.24</v>
       </c>
       <c r="Z3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA3">
         <v>928430000000</v>
       </c>
       <c r="AB3">
-        <v>35.02</v>
+        <v>35.020000000000003</v>
       </c>
       <c r="AC3">
-        <v>0.0068</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="AD3">
-        <v>583.92</v>
+        <v>583.91999999999996</v>
       </c>
       <c r="AE3">
         <v>3.39</v>
@@ -1038,135 +1075,143 @@
       <c r="AH3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="AI3">
+        <f t="shared" si="0"/>
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>44</v>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="6">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="3">
         <v>12742</v>
       </c>
-      <c r="H4" s="6">
-        <v>5.97E+24</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="H4">
+        <v>5.9700000000000003E+24</v>
+      </c>
+      <c r="I4" s="3">
         <v>149600000</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4">
         <v>365.25</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4">
         <v>23.9</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4">
         <v>1</v>
       </c>
-      <c r="N4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6" t="b">
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4">
         <v>15</v>
       </c>
-      <c r="Q4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="T4" s="6">
+      <c r="Q4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R4" t="s">
+        <v>77</v>
+      </c>
+      <c r="S4" t="s">
+        <v>83</v>
+      </c>
+      <c r="T4">
         <v>11.19</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4">
         <v>23.5</v>
       </c>
-      <c r="V4" s="6">
-        <v>0.367</v>
-      </c>
-      <c r="W4" s="6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="X4" s="6">
+      <c r="V4">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="W4">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="X4">
         <v>1</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4">
         <v>5.52</v>
       </c>
-      <c r="Z4" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA4" s="6">
+      <c r="Z4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA4">
         <v>1083210000000</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AB4">
         <v>29.78</v>
       </c>
-      <c r="AC4" s="6">
-        <v>0.0167</v>
-      </c>
-      <c r="AD4" s="6">
+      <c r="AC4">
+        <v>1.67E-2</v>
+      </c>
+      <c r="AD4">
         <v>365.25</v>
       </c>
-      <c r="AE4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>510000000</v>
       </c>
-      <c r="AG4" s="6">
+      <c r="AG4">
         <v>1361</v>
       </c>
-      <c r="AH4" s="6">
+      <c r="AH4">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3">
         <v>6779</v>
       </c>
       <c r="H5">
-        <v>6.39E+23</v>
+        <v>6.3899999999999998E+23</v>
       </c>
       <c r="I5" s="3">
         <v>227900000</v>
@@ -1193,13 +1238,13 @@
         <v>-65</v>
       </c>
       <c r="Q5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T5">
         <v>5.03</v>
@@ -1220,19 +1265,19 @@
         <v>3.93</v>
       </c>
       <c r="Z5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA5">
         <v>163180000000</v>
       </c>
       <c r="AB5">
-        <v>24.077</v>
+        <v>24.077000000000002</v>
       </c>
       <c r="AC5">
-        <v>0.0934</v>
+        <v>9.3399999999999997E-2</v>
       </c>
       <c r="AD5">
-        <v>779.9400000000001</v>
+        <v>779.94</v>
       </c>
       <c r="AE5">
         <v>1.85</v>
@@ -1246,31 +1291,35 @@
       <c r="AH5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>590.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3">
         <v>139820</v>
       </c>
       <c r="H6">
-        <v>1.9E+27</v>
+        <v>1.9000000000000001E+27</v>
       </c>
       <c r="I6" s="3">
         <v>778500000</v>
@@ -1297,13 +1346,13 @@
         <v>-110</v>
       </c>
       <c r="Q6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T6">
         <v>59.5</v>
@@ -1324,7 +1373,7 @@
         <v>1.33</v>
       </c>
       <c r="Z6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AA6">
         <v>1425000000000000</v>
@@ -1333,7 +1382,7 @@
         <v>13.07</v>
       </c>
       <c r="AC6">
-        <v>0.0489</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="AD6">
         <v>398.88</v>
@@ -1350,31 +1399,35 @@
       <c r="AH6">
         <v>417</v>
       </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>467.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3">
         <v>116460</v>
       </c>
       <c r="H7">
-        <v>5.68E+26</v>
+        <v>5.6800000000000001E+26</v>
       </c>
       <c r="I7" s="3">
         <v>1430000000</v>
@@ -1401,13 +1454,13 @@
         <v>-140</v>
       </c>
       <c r="Q7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T7">
         <v>35.5</v>
@@ -1425,10 +1478,10 @@
         <v>0.45</v>
       </c>
       <c r="Y7">
-        <v>0.6870000000000001</v>
+        <v>0.68700000000000006</v>
       </c>
       <c r="Z7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AA7">
         <v>827130000000000</v>
@@ -1437,13 +1490,13 @@
         <v>9.69</v>
       </c>
       <c r="AC7">
-        <v>0.0565</v>
+        <v>5.6500000000000002E-2</v>
       </c>
       <c r="AD7">
         <v>378.09</v>
       </c>
       <c r="AE7">
-        <v>2.485</v>
+        <v>2.4849999999999999</v>
       </c>
       <c r="AF7">
         <v>42700000000</v>
@@ -1454,31 +1507,35 @@
       <c r="AH7">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>10.899999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3">
         <v>50724</v>
       </c>
       <c r="H8">
-        <v>8.68E+25</v>
+        <v>8.6800000000000001E+25</v>
       </c>
       <c r="I8" s="3">
         <v>2870000000</v>
@@ -1505,13 +1562,13 @@
         <v>-195</v>
       </c>
       <c r="Q8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T8">
         <v>21.3</v>
@@ -1532,7 +1589,7 @@
         <v>1.27</v>
       </c>
       <c r="Z8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA8">
         <v>683300000000000</v>
@@ -1541,13 +1598,13 @@
         <v>6.81</v>
       </c>
       <c r="AC8">
-        <v>0.0463</v>
+        <v>4.6300000000000001E-2</v>
       </c>
       <c r="AD8">
         <v>369.66</v>
       </c>
       <c r="AE8">
-        <v>0.773</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="AF8">
         <v>8115000000</v>
@@ -1558,31 +1615,35 @@
       <c r="AH8">
         <v>25.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="3">
         <v>49244</v>
       </c>
       <c r="H9">
-        <v>1.02E+26</v>
+        <v>1.0200000000000001E+26</v>
       </c>
       <c r="I9" s="3">
         <v>4500000000</v>
@@ -1594,7 +1655,7 @@
         <v>60190</v>
       </c>
       <c r="L9">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="M9">
         <v>14</v>
@@ -1609,13 +1670,13 @@
         <v>-200</v>
       </c>
       <c r="Q9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T9">
         <v>23.5</v>
@@ -1636,7 +1697,7 @@
         <v>1.64</v>
       </c>
       <c r="Z9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA9">
         <v>625400000000000</v>
@@ -1645,13 +1706,13 @@
         <v>5.43</v>
       </c>
       <c r="AC9">
-        <v>0.0102</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="AD9">
         <v>367.49</v>
       </c>
       <c r="AE9">
-        <v>1.769</v>
+        <v>1.7689999999999999</v>
       </c>
       <c r="AF9">
         <v>7618000000</v>
@@ -1662,9 +1723,5953 @@
       <c r="AH9">
         <v>27.3</v>
       </c>
+      <c r="AI9">
+        <f t="shared" si="0"/>
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AI10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AI11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AI12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AI13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AI14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AI15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AI16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI49">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI66">
+        <f t="shared" ref="AI66:AI129" si="1">SUM(AG66, AH66)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI69">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI71">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI74">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI76">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI78">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI80">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI81">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI84">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI85">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI87">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI89">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI90">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI91">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI93">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI94">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI96">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI97">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI100">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI101">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI102">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI103">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI104">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI105">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI109">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI110">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI111">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI112">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI114">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI115">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI116">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI117">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI118">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI119">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI120">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI122">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI123">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI128">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI130">
+        <f t="shared" ref="AI130:AI193" si="2">SUM(AG130, AH130)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI131">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI132">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI134">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI135">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI136">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI137">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI139">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI140">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI141">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI143">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI144">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI145">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI146">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI148">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI151">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI153">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI154">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI156">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI157">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI158">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI159">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI160">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI161">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI162">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI163">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI164">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI165">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI168">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI169">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI170">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI171">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI172">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI173">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI174">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI175">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI176">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI177">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI178">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI179">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI180">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI181">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI182">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI183">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI184">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI185">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI186">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI187">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI188">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI189">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI190">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI191">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI192">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI193">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI194">
+        <f t="shared" ref="AI194:AI257" si="3">SUM(AG194, AH194)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI195">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI196">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI197">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI198">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI199">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI200">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI201">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI202">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI203">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI204">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI205">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI206">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI207">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI208">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI209">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI210">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI211">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI212">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI213">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI214">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI215">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI216">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI217">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI218">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI219">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI220">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI221">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI222">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI223">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI224">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI225">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI226">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI228">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI229">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI230">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI231">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI232">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI233">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI234">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI235">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI236">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI237">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI238">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI239">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI240">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI241">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI242">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI243">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI244">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI245">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI246">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI247">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI248">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI249">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI250">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI251">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI252">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI253">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI254">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI255">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI256">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI257">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI258">
+        <f t="shared" ref="AI258:AI321" si="4">SUM(AG258, AH258)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI259">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI260">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI261">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI262">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI263">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI264">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI265">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI266">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI267">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI268">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI269">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI270">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI271">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI272">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI273">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI274">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI275">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI276">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI277">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI278">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI279">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI280">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI281">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI282">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI283">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI284">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI285">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI286">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI287">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI288">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI289">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI290">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI291">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI292">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI293">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI294">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI295">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI296">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI297">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI298">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI299">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI300">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI301">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI302">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI303">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI304">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI305">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI306">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI307">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI308">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI309">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI310">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI311">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI312">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI313">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI314">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI315">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI316">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI317">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI318">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI319">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI320">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI321">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI322">
+        <f t="shared" ref="AI322:AI385" si="5">SUM(AG322, AH322)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI323">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI324">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI325">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI326">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI327">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI328">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI329">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI330">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI331">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI332">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI333">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI334">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI335">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI336">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI337">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI338">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI339">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI340">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI341">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI342">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI343">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI344">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI345">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI346">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI347">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI348">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI349">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI350">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI351">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI352">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI353">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI354">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI355">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI356">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI357">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI358">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI359">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI360">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI361">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI362">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI363">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI364">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI365">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI366">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI367">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI368">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI369">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI370">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI371">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI372">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI373">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI374">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI375">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI376">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI377">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI378">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI379">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI380">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI381">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI382">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI383">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI384">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI385">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI386">
+        <f t="shared" ref="AI386:AI449" si="6">SUM(AG386, AH386)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI387">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI388">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI389">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI390">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI391">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI392">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI393">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI394">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI395">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI396">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI397">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI398">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI399">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI400">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI401">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI402">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI403">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI404">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI405">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI406">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI407">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI408">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI409">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI410">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI411">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI412">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI413">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI414">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI415">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI416">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI417">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI418">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI419">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI420">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI421">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI422">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI423">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI424">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI425">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI426">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI427">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI428">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI429">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI430">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI431">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI432">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI433">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI434">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI435">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI436">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI437">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI438">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI439">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI440">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI441">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI442">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI443">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI444">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI445">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI446">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI447">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI448">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI449">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI450">
+        <f t="shared" ref="AI450:AI513" si="7">SUM(AG450, AH450)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI451">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI452">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI453">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI454">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI455">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI456">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI457">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI458">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI459">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI460">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI461">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI462">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI463">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI464">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI465">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI466">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI467">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI468">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI469">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI470">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI471">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI472">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI473">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI474">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI475">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI476">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI477">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI478">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI479">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI480">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI481">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI482">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI483">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI484">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI485">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI486">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI487">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI488">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI489">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI490">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI491">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI492">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI493">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI494">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI495">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI496">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI497">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI498">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI499">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI500">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI501">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI502">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI503">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI504">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI505">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI506">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI507">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI508">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI509">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI510">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI511">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI512">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI513">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI514">
+        <f t="shared" ref="AI514:AI577" si="8">SUM(AG514, AH514)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI515">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI516">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI517">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI518">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI519">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI520">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI521">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI522">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI523">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI524">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI525">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI526">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI527">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI528">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI529">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI530">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI531">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI532">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI533">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI534">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI535">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI536">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI537">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI538">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI539">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI540">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI541">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI542">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI543">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI544">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI545">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI546">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI547">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI548">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI549">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI550">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI551">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI552">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI553">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI554">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI555">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI556">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI557">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI558">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI559">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI560">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI561">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI562">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI563">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI564">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI565">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI566">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI567">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI568">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI569">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI570">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI571">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI572">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI573">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI574">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI575">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI576">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI577">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI578">
+        <f t="shared" ref="AI578:AI641" si="9">SUM(AG578, AH578)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI579">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI580">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI581">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI582">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI583">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI584">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI585">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI586">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI587">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI588">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI589">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI590">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI591">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI592">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI593">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI594">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI595">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI596">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI597">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI598">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI599">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI600">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI601">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI602">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI603">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI604">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI605">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI606">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI607">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI608">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI609">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI610">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI611">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI612">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI613">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI614">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI615">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI616">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI617">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI618">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI619">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI620">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI621">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI622">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI623">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI624">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI625">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI626">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI627">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI628">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI629">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI630">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI631">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI632">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI633">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI634">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI635">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI636">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI637">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI638">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI639">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI640">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI641">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI642">
+        <f t="shared" ref="AI642:AI705" si="10">SUM(AG642, AH642)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI643">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI644">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI645">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI646">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI647">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI648">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI649">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI650">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI651">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI652">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI653">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI654">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI655">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI656">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI657">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI658">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI659">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI660">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI661">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI662">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI663">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI664">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI665">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI666">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI667">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI668">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI669">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI670">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI671">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI672">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI673">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI674">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI675">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI676">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI677">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI678">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI679">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI680">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI681">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI682">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI683">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI684">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI685">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI686">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI687">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI688">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI689">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI690">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI691">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI692">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI693">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI694">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI695">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI696">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI697">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI698">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI699">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI700">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI701">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI702">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI703">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI704">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI705">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI706">
+        <f t="shared" ref="AI706:AI769" si="11">SUM(AG706, AH706)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI707">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI708">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI709">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI710">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI711">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI712">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI713">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI714">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI715">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI716">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI717">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI718">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI719">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI720">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI721">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI722">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI723">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI724">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI725">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI726">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI727">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI728">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI729">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI730">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI731">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI732">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI733">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI734">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI735">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI736">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI737">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI738">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI739">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI740">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI741">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI742">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI743">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI744">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI745">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI746">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI747">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI748">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI749">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI750">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI751">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI752">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI753">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI754">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI755">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI756">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI757">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI758">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI759">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI760">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI761">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI762">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI763">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI764">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI765">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI766">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI767">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI768">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI769">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI770">
+        <f t="shared" ref="AI770:AI833" si="12">SUM(AG770, AH770)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI771">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI772">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI773">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI774">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI775">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI776">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI777">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI778">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI779">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI780">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI781">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI782">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI783">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI784">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI785">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI786">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI787">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI788">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI789">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI790">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI791">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI792">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI793">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI794">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI795">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI796">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI797">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI798">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI799">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI800">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI801">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI802">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI803">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI804">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI805">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI806">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI807">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI808">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI809">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI810">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI811">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI812">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI813">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI814">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI815">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI816">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI817">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI818">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI819">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI820">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI821">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI822">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI823">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI824">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI825">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI826">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI827">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI828">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI829">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI830">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI831">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI832">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI833">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI834">
+        <f t="shared" ref="AI834:AI897" si="13">SUM(AG834, AH834)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI835">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI836">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI837">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI838">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI839">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI840">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI841">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI842">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI843">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI844">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI845">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI846">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI847">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI848">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI849">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI850">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI851">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI852">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI853">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI854">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI855">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI856">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI857">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI858">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI859">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI860">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI861">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI862">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI863">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI864">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI865">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI866">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI867">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI868">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI869">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI870">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI871">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI872">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI873">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI874">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI875">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI876">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI877">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI878">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI879">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI880">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI881">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI882">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI883">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI884">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI885">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI886">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI887">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI888">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI889">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI890">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI891">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI892">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI893">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI894">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI895">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI896">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI897">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI898">
+        <f t="shared" ref="AI898:AI961" si="14">SUM(AG898, AH898)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI899">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI900">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI901">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI902">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI903">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI904">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI905">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI906">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI907">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI908">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="909" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI909">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI910">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI911">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI912">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI913">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI914">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI915">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI916">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI917">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI918">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI919">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI920">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI921">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI922">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI923">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI924">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI925">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI926">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI927">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI928">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI929">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="930" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI930">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI931">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI932">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI933">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI934">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI935">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI936">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI937">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI938">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI939">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI940">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI941">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI942">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI943">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI944">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="945" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI945">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI946">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI947">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="948" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI948">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI949">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI950">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI951">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI952">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI953">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI954">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="955" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI955">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="956" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI956">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="957" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI957">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI958">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="959" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI959">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="960" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI960">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="961" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI961">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI962">
+        <f t="shared" ref="AI962:AI1025" si="15">SUM(AG962, AH962)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="963" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI963">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI964">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI965">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI966">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI967">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI968">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI969">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI970">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI971">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="972" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI972">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="973" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI973">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="974" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI974">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="975" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI975">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="976" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI976">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="977" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI977">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="978" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI978">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI979">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="980" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI980">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="981" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI981">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI982">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="983" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI983">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI984">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI985">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI986">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI987">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI988">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="989" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI989">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI990">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI991">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="992" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI992">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="993" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI993">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI994">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="995" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI995">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI996">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI997">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI998">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999" spans="35:35" x14ac:dyDescent="0.25">
+      <c r="AI999">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AH9"/>
+  <autoFilter ref="A1:AI9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="G2:G10000">
     <cfRule type="dataBar" priority="1">
       <dataBar>
@@ -1682,15 +7687,33 @@
   <conditionalFormatting sqref="I2:I10000">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="max" val="0"/>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFA91B0D"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M10000">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFFF6C74"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:O10000">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",N2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",N2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P10000">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="9">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1703,15 +7726,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R10000">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="oxygen">
+      <formula>NOT(ISERROR(SEARCH("oxygen",R2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="D4" r:id="rId3"/>
-    <hyperlink ref="D5" r:id="rId4"/>
-    <hyperlink ref="D6" r:id="rId5"/>
-    <hyperlink ref="D7" r:id="rId6"/>
-    <hyperlink ref="D8" r:id="rId7"/>
-    <hyperlink ref="D9" r:id="rId8"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>

--- a/example_datasets/planets-info/planets_data_proc.xlsx
+++ b/example_datasets/planets-info/planets_data_proc.xlsx
@@ -1,29 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evgen\Desktop\Handbook_Data-Science\example_datasets\planets-info\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61C3774-CCC2-4563-959F-CAE4537D69B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="300"/>
   </bookViews>
   <sheets>
-    <sheet name="main" sheetId="1" r:id="rId1"/>
+    <sheet name="intro" sheetId="1" r:id="rId1"/>
+    <sheet name="main" sheetId="2" r:id="rId2"/>
+    <sheet name="plots" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$AI$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">main!$A$1:$AI$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="96">
+  <si>
+    <t xml:space="preserve">      Title here</t>
+  </si>
   <si>
     <t>planetOrder</t>
   </si>
@@ -313,11 +312,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF333333"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,6 +340,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -338,15 +355,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF951F06"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -354,44 +377,33 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -408,32 +420,237 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF008000"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FF008000"/>
+        <color rgb="FFFF0000"/>
       </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="5"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Escape velocity and gravity</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>chartName</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>main!$T$2:$T$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>59.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>main!$W$2:$W$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.869999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.71</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.79</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.44</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.69</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>escape_velocity_km_s</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>gravity_m_s2</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -471,7 +688,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -505,7 +722,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -540,10 +756,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -716,180 +931,242 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AS1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AS1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AI999"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="80.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="46.7109375" customWidth="1"/>
-    <col min="5" max="5" width="80.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="27.7109375" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="21.7109375" customWidth="1"/>
-    <col min="16" max="16" width="27.7109375" customWidth="1"/>
-    <col min="17" max="17" width="21.7109375" customWidth="1"/>
-    <col min="18" max="18" width="39.7109375" customWidth="1"/>
-    <col min="19" max="19" width="43.7109375" customWidth="1"/>
-    <col min="20" max="20" width="20.7109375" customWidth="1"/>
-    <col min="21" max="21" width="18.7109375" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" customWidth="1"/>
-    <col min="23" max="23" width="12.7109375" customWidth="1"/>
-    <col min="24" max="24" width="21.7109375" customWidth="1"/>
-    <col min="25" max="25" width="13.7109375" customWidth="1"/>
-    <col min="26" max="26" width="30.7109375" customWidth="1"/>
-    <col min="27" max="27" width="18.7109375" customWidth="1"/>
-    <col min="28" max="28" width="23.7109375" customWidth="1"/>
-    <col min="29" max="29" width="20.7109375" customWidth="1"/>
-    <col min="30" max="30" width="19.7109375" customWidth="1"/>
-    <col min="31" max="31" width="27.7109375" customWidth="1"/>
-    <col min="32" max="32" width="16.7109375" customWidth="1"/>
-    <col min="33" max="33" width="19.7109375" customWidth="1"/>
-    <col min="34" max="34" width="26.7109375" customWidth="1"/>
-    <col min="35" max="35" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="85.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="51.7109375" customWidth="1"/>
+    <col min="5" max="5" width="85.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="32.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" customWidth="1"/>
+    <col min="16" max="16" width="32.7109375" customWidth="1"/>
+    <col min="17" max="17" width="26.7109375" customWidth="1"/>
+    <col min="18" max="18" width="44.7109375" customWidth="1"/>
+    <col min="19" max="19" width="48.7109375" customWidth="1"/>
+    <col min="20" max="20" width="25.7109375" customWidth="1"/>
+    <col min="21" max="21" width="23.7109375" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" customWidth="1"/>
+    <col min="23" max="23" width="17.7109375" customWidth="1"/>
+    <col min="24" max="24" width="26.7109375" customWidth="1"/>
+    <col min="25" max="25" width="18.7109375" customWidth="1"/>
+    <col min="26" max="26" width="35.7109375" customWidth="1"/>
+    <col min="27" max="27" width="23.7109375" customWidth="1"/>
+    <col min="28" max="28" width="28.7109375" customWidth="1"/>
+    <col min="29" max="29" width="25.7109375" customWidth="1"/>
+    <col min="30" max="30" width="24.7109375" customWidth="1"/>
+    <col min="31" max="31" width="32.7109375" customWidth="1"/>
+    <col min="32" max="32" width="21.7109375" customWidth="1"/>
+    <col min="33" max="33" width="24.7109375" customWidth="1"/>
+    <col min="34" max="34" width="31.7109375" customWidth="1"/>
+    <col min="35" max="35" width="45.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="N1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="O1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="P1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="Q1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="R1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="S1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="T1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="U1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="V1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="W1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="X1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Y1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="Z1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AA1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AB1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AC1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AD1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AE1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AF1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AG1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AH1" s="6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="AI1" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>51</v>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="3">
+        <v>68</v>
+      </c>
+      <c r="G2" s="5">
         <v>4879</v>
       </c>
       <c r="H2">
-        <v>3.3000000000000003E+23</v>
-      </c>
-      <c r="I2" s="3">
+        <v>3.3E+23</v>
+      </c>
+      <c r="I2" s="5">
         <v>57900000</v>
       </c>
       <c r="J2">
@@ -914,22 +1191,22 @@
         <v>167</v>
       </c>
       <c r="Q2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T2">
         <v>4.25</v>
       </c>
       <c r="U2">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="V2">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="W2">
         <v>3.7</v>
@@ -941,7 +1218,7 @@
         <v>5.43</v>
       </c>
       <c r="Z2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA2">
         <v>60830000000</v>
@@ -968,36 +1245,36 @@
         <v>0.3</v>
       </c>
       <c r="AI2">
-        <f t="shared" ref="AI2:AI65" si="0">SUM(AG2, AH2)</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+        <f>SUM(AG2, AH2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>52</v>
+      <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="3">
+        <v>68</v>
+      </c>
+      <c r="G3" s="5">
         <v>12104</v>
       </c>
       <c r="H3">
-        <v>4.8699999999999996E+24</v>
-      </c>
-      <c r="I3" s="3">
+        <v>4.87E+24</v>
+      </c>
+      <c r="I3" s="5">
         <v>108200000</v>
       </c>
       <c r="J3">
@@ -1022,13 +1299,13 @@
         <v>464</v>
       </c>
       <c r="Q3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T3">
         <v>10.36</v>
@@ -1040,7 +1317,7 @@
         <v>0.75</v>
       </c>
       <c r="W3">
-        <v>8.8699999999999992</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="X3">
         <v>243</v>
@@ -1049,19 +1326,19 @@
         <v>5.24</v>
       </c>
       <c r="Z3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA3">
         <v>928430000000</v>
       </c>
       <c r="AB3">
-        <v>35.020000000000003</v>
+        <v>35.02</v>
       </c>
       <c r="AC3">
-        <v>6.7999999999999996E-3</v>
+        <v>0.0068</v>
       </c>
       <c r="AD3">
-        <v>583.91999999999996</v>
+        <v>583.92</v>
       </c>
       <c r="AE3">
         <v>3.39</v>
@@ -1076,36 +1353,36 @@
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" si="0"/>
-        <v>2610</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+        <f>SUM(AG3, AH3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>53</v>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="3">
+        <v>68</v>
+      </c>
+      <c r="G4" s="5">
         <v>12742</v>
       </c>
       <c r="H4">
-        <v>5.9700000000000003E+24</v>
-      </c>
-      <c r="I4" s="3">
+        <v>5.97E+24</v>
+      </c>
+      <c r="I4" s="5">
         <v>149600000</v>
       </c>
       <c r="J4">
@@ -1130,13 +1407,13 @@
         <v>15</v>
       </c>
       <c r="Q4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T4">
         <v>11.19</v>
@@ -1145,10 +1422,10 @@
         <v>23.5</v>
       </c>
       <c r="V4">
-        <v>0.36699999999999999</v>
+        <v>0.367</v>
       </c>
       <c r="W4">
-        <v>9.8000000000000007</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -1157,7 +1434,7 @@
         <v>5.52</v>
       </c>
       <c r="Z4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA4">
         <v>1083210000000</v>
@@ -1166,7 +1443,7 @@
         <v>29.78</v>
       </c>
       <c r="AC4">
-        <v>1.67E-2</v>
+        <v>0.0167</v>
       </c>
       <c r="AD4">
         <v>365.25</v>
@@ -1184,36 +1461,36 @@
         <v>25</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="0"/>
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+        <f>SUM(AG4, AH4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>54</v>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="3">
+        <v>68</v>
+      </c>
+      <c r="G5" s="5">
         <v>6779</v>
       </c>
       <c r="H5">
-        <v>6.3899999999999998E+23</v>
-      </c>
-      <c r="I5" s="3">
+        <v>6.39E+23</v>
+      </c>
+      <c r="I5" s="5">
         <v>227900000</v>
       </c>
       <c r="J5">
@@ -1238,13 +1515,13 @@
         <v>-65</v>
       </c>
       <c r="Q5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T5">
         <v>5.03</v>
@@ -1265,19 +1542,19 @@
         <v>3.93</v>
       </c>
       <c r="Z5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AA5">
         <v>163180000000</v>
       </c>
       <c r="AB5">
-        <v>24.077000000000002</v>
+        <v>24.077</v>
       </c>
       <c r="AC5">
-        <v>9.3399999999999997E-2</v>
+        <v>0.0934</v>
       </c>
       <c r="AD5">
-        <v>779.94</v>
+        <v>779.9400000000001</v>
       </c>
       <c r="AE5">
         <v>1.85</v>
@@ -1292,36 +1569,36 @@
         <v>0.1</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="0"/>
-        <v>590.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+        <f>SUM(AG5, AH5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="3">
+        <v>69</v>
+      </c>
+      <c r="G6" s="5">
         <v>139820</v>
       </c>
       <c r="H6">
-        <v>1.9000000000000001E+27</v>
-      </c>
-      <c r="I6" s="3">
+        <v>1.9E+27</v>
+      </c>
+      <c r="I6" s="5">
         <v>778500000</v>
       </c>
       <c r="J6">
@@ -1346,13 +1623,13 @@
         <v>-110</v>
       </c>
       <c r="Q6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T6">
         <v>59.5</v>
@@ -1373,7 +1650,7 @@
         <v>1.33</v>
       </c>
       <c r="Z6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA6">
         <v>1425000000000000</v>
@@ -1382,7 +1659,7 @@
         <v>13.07</v>
       </c>
       <c r="AC6">
-        <v>4.8899999999999999E-2</v>
+        <v>0.0489</v>
       </c>
       <c r="AD6">
         <v>398.88</v>
@@ -1400,36 +1677,36 @@
         <v>417</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="0"/>
-        <v>467.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+        <f>SUM(AG6, AH6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>56</v>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="3">
+        <v>69</v>
+      </c>
+      <c r="G7" s="5">
         <v>116460</v>
       </c>
       <c r="H7">
-        <v>5.6800000000000001E+26</v>
-      </c>
-      <c r="I7" s="3">
+        <v>5.68E+26</v>
+      </c>
+      <c r="I7" s="5">
         <v>1430000000</v>
       </c>
       <c r="J7">
@@ -1454,13 +1731,13 @@
         <v>-140</v>
       </c>
       <c r="Q7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T7">
         <v>35.5</v>
@@ -1478,10 +1755,10 @@
         <v>0.45</v>
       </c>
       <c r="Y7">
-        <v>0.68700000000000006</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="Z7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA7">
         <v>827130000000000</v>
@@ -1490,13 +1767,13 @@
         <v>9.69</v>
       </c>
       <c r="AC7">
-        <v>5.6500000000000002E-2</v>
+        <v>0.0565</v>
       </c>
       <c r="AD7">
         <v>378.09</v>
       </c>
       <c r="AE7">
-        <v>2.4849999999999999</v>
+        <v>2.485</v>
       </c>
       <c r="AF7">
         <v>42700000000</v>
@@ -1508,36 +1785,36 @@
         <v>0.2</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="0"/>
-        <v>10.899999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+        <f>SUM(AG7, AH7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>57</v>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="3">
+        <v>70</v>
+      </c>
+      <c r="G8" s="5">
         <v>50724</v>
       </c>
       <c r="H8">
-        <v>8.6800000000000001E+25</v>
-      </c>
-      <c r="I8" s="3">
+        <v>8.68E+25</v>
+      </c>
+      <c r="I8" s="5">
         <v>2870000000</v>
       </c>
       <c r="J8">
@@ -1562,13 +1839,13 @@
         <v>-195</v>
       </c>
       <c r="Q8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T8">
         <v>21.3</v>
@@ -1589,7 +1866,7 @@
         <v>1.27</v>
       </c>
       <c r="Z8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA8">
         <v>683300000000000</v>
@@ -1598,13 +1875,13 @@
         <v>6.81</v>
       </c>
       <c r="AC8">
-        <v>4.6300000000000001E-2</v>
+        <v>0.0463</v>
       </c>
       <c r="AD8">
         <v>369.66</v>
       </c>
       <c r="AE8">
-        <v>0.77300000000000002</v>
+        <v>0.773</v>
       </c>
       <c r="AF8">
         <v>8115000000</v>
@@ -1616,36 +1893,36 @@
         <v>25.7</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="0"/>
-        <v>29.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+        <f>SUM(AG8, AH8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>58</v>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="3">
+        <v>70</v>
+      </c>
+      <c r="G9" s="5">
         <v>49244</v>
       </c>
       <c r="H9">
-        <v>1.0200000000000001E+26</v>
-      </c>
-      <c r="I9" s="3">
+        <v>1.02E+26</v>
+      </c>
+      <c r="I9" s="5">
         <v>4500000000</v>
       </c>
       <c r="J9">
@@ -1655,7 +1932,7 @@
         <v>60190</v>
       </c>
       <c r="L9">
-        <v>16.100000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="M9">
         <v>14</v>
@@ -1670,13 +1947,13 @@
         <v>-200</v>
       </c>
       <c r="Q9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="T9">
         <v>23.5</v>
@@ -1697,7 +1974,7 @@
         <v>1.64</v>
       </c>
       <c r="Z9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA9">
         <v>625400000000000</v>
@@ -1706,13 +1983,13 @@
         <v>5.43</v>
       </c>
       <c r="AC9">
-        <v>1.0200000000000001E-2</v>
+        <v>0.0102</v>
       </c>
       <c r="AD9">
         <v>367.49</v>
       </c>
       <c r="AE9">
-        <v>1.7689999999999999</v>
+        <v>1.769</v>
       </c>
       <c r="AF9">
         <v>7618000000</v>
@@ -1724,5952 +2001,5952 @@
         <v>27.3</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="0"/>
-        <v>28.8</v>
+        <f>SUM(AG9, AH9)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="AI10">
-        <f t="shared" si="0"/>
+        <f>SUM(AG10, AH10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="AI11">
-        <f t="shared" si="0"/>
+        <f>SUM(AG11, AH11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="AI12">
-        <f t="shared" si="0"/>
+        <f>SUM(AG12, AH12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="AI13">
-        <f t="shared" si="0"/>
+        <f>SUM(AG13, AH13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="AI14">
-        <f t="shared" si="0"/>
+        <f>SUM(AG14, AH14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="AI15">
-        <f t="shared" si="0"/>
+        <f>SUM(AG15, AH15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="AI16">
-        <f t="shared" si="0"/>
+        <f>SUM(AG16, AH16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI17">
-        <f t="shared" si="0"/>
+        <f>SUM(AG17, AH17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI18">
-        <f t="shared" si="0"/>
+        <f>SUM(AG18, AH18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI19">
-        <f t="shared" si="0"/>
+        <f>SUM(AG19, AH19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI20">
-        <f t="shared" si="0"/>
+        <f>SUM(AG20, AH20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI21">
-        <f t="shared" si="0"/>
+        <f>SUM(AG21, AH21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI22">
-        <f t="shared" si="0"/>
+        <f>SUM(AG22, AH22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI23">
-        <f t="shared" si="0"/>
+        <f>SUM(AG23, AH23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI24">
-        <f t="shared" si="0"/>
+        <f>SUM(AG24, AH24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI25">
-        <f t="shared" si="0"/>
+        <f>SUM(AG25, AH25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI26">
-        <f t="shared" si="0"/>
+        <f>SUM(AG26, AH26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI27">
-        <f t="shared" si="0"/>
+        <f>SUM(AG27, AH27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI28">
-        <f t="shared" si="0"/>
+        <f>SUM(AG28, AH28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI29">
-        <f t="shared" si="0"/>
+        <f>SUM(AG29, AH29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI30">
-        <f t="shared" si="0"/>
+        <f>SUM(AG30, AH30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI31">
-        <f t="shared" si="0"/>
+        <f>SUM(AG31, AH31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI32">
-        <f t="shared" si="0"/>
+        <f>SUM(AG32, AH32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI33">
-        <f t="shared" si="0"/>
+        <f>SUM(AG33, AH33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI34">
-        <f t="shared" si="0"/>
+        <f>SUM(AG34, AH34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI35">
-        <f t="shared" si="0"/>
+        <f>SUM(AG35, AH35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI36">
-        <f t="shared" si="0"/>
+        <f>SUM(AG36, AH36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI37">
-        <f t="shared" si="0"/>
+        <f>SUM(AG37, AH37)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI38">
-        <f t="shared" si="0"/>
+        <f>SUM(AG38, AH38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI39">
-        <f t="shared" si="0"/>
+        <f>SUM(AG39, AH39)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI40">
-        <f t="shared" si="0"/>
+        <f>SUM(AG40, AH40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI41">
-        <f t="shared" si="0"/>
+        <f>SUM(AG41, AH41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI42">
-        <f t="shared" si="0"/>
+        <f>SUM(AG42, AH42)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI43">
-        <f t="shared" si="0"/>
+        <f>SUM(AG43, AH43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI44">
-        <f t="shared" si="0"/>
+        <f>SUM(AG44, AH44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI45">
-        <f t="shared" si="0"/>
+        <f>SUM(AG45, AH45)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI46">
-        <f t="shared" si="0"/>
+        <f>SUM(AG46, AH46)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI47">
-        <f t="shared" si="0"/>
+        <f>SUM(AG47, AH47)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI48">
-        <f t="shared" si="0"/>
+        <f>SUM(AG48, AH48)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI49">
-        <f t="shared" si="0"/>
+        <f>SUM(AG49, AH49)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI50">
-        <f t="shared" si="0"/>
+        <f>SUM(AG50, AH50)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI51">
-        <f t="shared" si="0"/>
+        <f>SUM(AG51, AH51)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI52">
-        <f t="shared" si="0"/>
+        <f>SUM(AG52, AH52)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI53">
-        <f t="shared" si="0"/>
+        <f>SUM(AG53, AH53)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI54">
-        <f t="shared" si="0"/>
+        <f>SUM(AG54, AH54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI55">
-        <f t="shared" si="0"/>
+        <f>SUM(AG55, AH55)</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI56">
-        <f t="shared" si="0"/>
+        <f>SUM(AG56, AH56)</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI57">
-        <f t="shared" si="0"/>
+        <f>SUM(AG57, AH57)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI58">
-        <f t="shared" si="0"/>
+        <f>SUM(AG58, AH58)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI59">
-        <f t="shared" si="0"/>
+        <f>SUM(AG59, AH59)</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI60">
-        <f t="shared" si="0"/>
+        <f>SUM(AG60, AH60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI61">
-        <f t="shared" si="0"/>
+        <f>SUM(AG61, AH61)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI62">
-        <f t="shared" si="0"/>
+        <f>SUM(AG62, AH62)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI63">
-        <f t="shared" si="0"/>
+        <f>SUM(AG63, AH63)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI64">
-        <f t="shared" si="0"/>
+        <f>SUM(AG64, AH64)</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI65">
-        <f t="shared" si="0"/>
+        <f>SUM(AG65, AH65)</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI66">
-        <f t="shared" ref="AI66:AI129" si="1">SUM(AG66, AH66)</f>
+        <f>SUM(AG66, AH66)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI67">
-        <f t="shared" si="1"/>
+        <f>SUM(AG67, AH67)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI68">
-        <f t="shared" si="1"/>
+        <f>SUM(AG68, AH68)</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI69">
-        <f t="shared" si="1"/>
+        <f>SUM(AG69, AH69)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI70">
-        <f t="shared" si="1"/>
+        <f>SUM(AG70, AH70)</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI71">
-        <f t="shared" si="1"/>
+        <f>SUM(AG71, AH71)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI72">
-        <f t="shared" si="1"/>
+        <f>SUM(AG72, AH72)</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI73">
-        <f t="shared" si="1"/>
+        <f>SUM(AG73, AH73)</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI74">
-        <f t="shared" si="1"/>
+        <f>SUM(AG74, AH74)</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI75">
-        <f t="shared" si="1"/>
+        <f>SUM(AG75, AH75)</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI76">
-        <f t="shared" si="1"/>
+        <f>SUM(AG76, AH76)</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI77">
-        <f t="shared" si="1"/>
+        <f>SUM(AG77, AH77)</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI78">
-        <f t="shared" si="1"/>
+        <f>SUM(AG78, AH78)</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI79">
-        <f t="shared" si="1"/>
+        <f>SUM(AG79, AH79)</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI80">
-        <f t="shared" si="1"/>
+        <f>SUM(AG80, AH80)</f>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI81">
-        <f t="shared" si="1"/>
+        <f>SUM(AG81, AH81)</f>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI82">
-        <f t="shared" si="1"/>
+        <f>SUM(AG82, AH82)</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI83">
-        <f t="shared" si="1"/>
+        <f>SUM(AG83, AH83)</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI84">
-        <f t="shared" si="1"/>
+        <f>SUM(AG84, AH84)</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI85">
-        <f t="shared" si="1"/>
+        <f>SUM(AG85, AH85)</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI86">
-        <f t="shared" si="1"/>
+        <f>SUM(AG86, AH86)</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI87">
-        <f t="shared" si="1"/>
+        <f>SUM(AG87, AH87)</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI88">
-        <f t="shared" si="1"/>
+        <f>SUM(AG88, AH88)</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI89">
-        <f t="shared" si="1"/>
+        <f>SUM(AG89, AH89)</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI90">
-        <f t="shared" si="1"/>
+        <f>SUM(AG90, AH90)</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI91">
-        <f t="shared" si="1"/>
+        <f>SUM(AG91, AH91)</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI92">
-        <f t="shared" si="1"/>
+        <f>SUM(AG92, AH92)</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI93">
-        <f t="shared" si="1"/>
+        <f>SUM(AG93, AH93)</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI94">
-        <f t="shared" si="1"/>
+        <f>SUM(AG94, AH94)</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI95">
-        <f t="shared" si="1"/>
+        <f>SUM(AG95, AH95)</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI96">
-        <f t="shared" si="1"/>
+        <f>SUM(AG96, AH96)</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI97">
-        <f t="shared" si="1"/>
+        <f>SUM(AG97, AH97)</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI98">
-        <f t="shared" si="1"/>
+        <f>SUM(AG98, AH98)</f>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI99">
-        <f t="shared" si="1"/>
+        <f>SUM(AG99, AH99)</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI100">
-        <f t="shared" si="1"/>
+        <f>SUM(AG100, AH100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI101">
-        <f t="shared" si="1"/>
+        <f>SUM(AG101, AH101)</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI102">
-        <f t="shared" si="1"/>
+        <f>SUM(AG102, AH102)</f>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI103">
-        <f t="shared" si="1"/>
+        <f>SUM(AG103, AH103)</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI104">
-        <f t="shared" si="1"/>
+        <f>SUM(AG104, AH104)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI105">
-        <f t="shared" si="1"/>
+        <f>SUM(AG105, AH105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI106">
-        <f t="shared" si="1"/>
+        <f>SUM(AG106, AH106)</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI107">
-        <f t="shared" si="1"/>
+        <f>SUM(AG107, AH107)</f>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI108">
-        <f t="shared" si="1"/>
+        <f>SUM(AG108, AH108)</f>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI109">
-        <f t="shared" si="1"/>
+        <f>SUM(AG109, AH109)</f>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI110">
-        <f t="shared" si="1"/>
+        <f>SUM(AG110, AH110)</f>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI111">
-        <f t="shared" si="1"/>
+        <f>SUM(AG111, AH111)</f>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI112">
-        <f t="shared" si="1"/>
+        <f>SUM(AG112, AH112)</f>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI113">
-        <f t="shared" si="1"/>
+        <f>SUM(AG113, AH113)</f>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI114">
-        <f t="shared" si="1"/>
+        <f>SUM(AG114, AH114)</f>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI115">
-        <f t="shared" si="1"/>
+        <f>SUM(AG115, AH115)</f>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI116">
-        <f t="shared" si="1"/>
+        <f>SUM(AG116, AH116)</f>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI117">
-        <f t="shared" si="1"/>
+        <f>SUM(AG117, AH117)</f>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI118">
-        <f t="shared" si="1"/>
+        <f>SUM(AG118, AH118)</f>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI119">
-        <f t="shared" si="1"/>
+        <f>SUM(AG119, AH119)</f>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI120">
-        <f t="shared" si="1"/>
+        <f>SUM(AG120, AH120)</f>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI121">
-        <f t="shared" si="1"/>
+        <f>SUM(AG121, AH121)</f>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI122">
-        <f t="shared" si="1"/>
+        <f>SUM(AG122, AH122)</f>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI123">
-        <f t="shared" si="1"/>
+        <f>SUM(AG123, AH123)</f>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI124">
-        <f t="shared" si="1"/>
+        <f>SUM(AG124, AH124)</f>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI125">
-        <f t="shared" si="1"/>
+        <f>SUM(AG125, AH125)</f>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI126">
-        <f t="shared" si="1"/>
+        <f>SUM(AG126, AH126)</f>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI127">
-        <f t="shared" si="1"/>
+        <f>SUM(AG127, AH127)</f>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI128">
-        <f t="shared" si="1"/>
+        <f>SUM(AG128, AH128)</f>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI129">
-        <f t="shared" si="1"/>
+        <f>SUM(AG129, AH129)</f>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI130">
-        <f t="shared" ref="AI130:AI193" si="2">SUM(AG130, AH130)</f>
+        <f>SUM(AG130, AH130)</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI131">
-        <f t="shared" si="2"/>
+        <f>SUM(AG131, AH131)</f>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI132">
-        <f t="shared" si="2"/>
+        <f>SUM(AG132, AH132)</f>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI133">
-        <f t="shared" si="2"/>
+        <f>SUM(AG133, AH133)</f>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI134">
-        <f t="shared" si="2"/>
+        <f>SUM(AG134, AH134)</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI135">
-        <f t="shared" si="2"/>
+        <f>SUM(AG135, AH135)</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI136">
-        <f t="shared" si="2"/>
+        <f>SUM(AG136, AH136)</f>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI137">
-        <f t="shared" si="2"/>
+        <f>SUM(AG137, AH137)</f>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI138">
-        <f t="shared" si="2"/>
+        <f>SUM(AG138, AH138)</f>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI139">
-        <f t="shared" si="2"/>
+        <f>SUM(AG139, AH139)</f>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI140">
-        <f t="shared" si="2"/>
+        <f>SUM(AG140, AH140)</f>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI141">
-        <f t="shared" si="2"/>
+        <f>SUM(AG141, AH141)</f>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI142">
-        <f t="shared" si="2"/>
+        <f>SUM(AG142, AH142)</f>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI143">
-        <f t="shared" si="2"/>
+        <f>SUM(AG143, AH143)</f>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI144">
-        <f t="shared" si="2"/>
+        <f>SUM(AG144, AH144)</f>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI145">
-        <f t="shared" si="2"/>
+        <f>SUM(AG145, AH145)</f>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI146">
-        <f t="shared" si="2"/>
+        <f>SUM(AG146, AH146)</f>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI147">
-        <f t="shared" si="2"/>
+        <f>SUM(AG147, AH147)</f>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI148">
-        <f t="shared" si="2"/>
+        <f>SUM(AG148, AH148)</f>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI149">
-        <f t="shared" si="2"/>
+        <f>SUM(AG149, AH149)</f>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI150">
-        <f t="shared" si="2"/>
+        <f>SUM(AG150, AH150)</f>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI151">
-        <f t="shared" si="2"/>
+        <f>SUM(AG151, AH151)</f>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI152">
-        <f t="shared" si="2"/>
+        <f>SUM(AG152, AH152)</f>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI153">
-        <f t="shared" si="2"/>
+        <f>SUM(AG153, AH153)</f>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI154">
-        <f t="shared" si="2"/>
+        <f>SUM(AG154, AH154)</f>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI155">
-        <f t="shared" si="2"/>
+        <f>SUM(AG155, AH155)</f>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI156">
-        <f t="shared" si="2"/>
+        <f>SUM(AG156, AH156)</f>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI157">
-        <f t="shared" si="2"/>
+        <f>SUM(AG157, AH157)</f>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI158">
-        <f t="shared" si="2"/>
+        <f>SUM(AG158, AH158)</f>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI159">
-        <f t="shared" si="2"/>
+        <f>SUM(AG159, AH159)</f>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI160">
-        <f t="shared" si="2"/>
+        <f>SUM(AG160, AH160)</f>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI161">
-        <f t="shared" si="2"/>
+        <f>SUM(AG161, AH161)</f>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI162">
-        <f t="shared" si="2"/>
+        <f>SUM(AG162, AH162)</f>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI163">
-        <f t="shared" si="2"/>
+        <f>SUM(AG163, AH163)</f>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI164">
-        <f t="shared" si="2"/>
+        <f>SUM(AG164, AH164)</f>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI165">
-        <f t="shared" si="2"/>
+        <f>SUM(AG165, AH165)</f>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI166">
-        <f t="shared" si="2"/>
+        <f>SUM(AG166, AH166)</f>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI167">
-        <f t="shared" si="2"/>
+        <f>SUM(AG167, AH167)</f>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI168">
-        <f t="shared" si="2"/>
+        <f>SUM(AG168, AH168)</f>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI169">
-        <f t="shared" si="2"/>
+        <f>SUM(AG169, AH169)</f>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI170">
-        <f t="shared" si="2"/>
+        <f>SUM(AG170, AH170)</f>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI171">
-        <f t="shared" si="2"/>
+        <f>SUM(AG171, AH171)</f>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI172">
-        <f t="shared" si="2"/>
+        <f>SUM(AG172, AH172)</f>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI173">
-        <f t="shared" si="2"/>
+        <f>SUM(AG173, AH173)</f>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI174">
-        <f t="shared" si="2"/>
+        <f>SUM(AG174, AH174)</f>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI175">
-        <f t="shared" si="2"/>
+        <f>SUM(AG175, AH175)</f>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI176">
-        <f t="shared" si="2"/>
+        <f>SUM(AG176, AH176)</f>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI177">
-        <f t="shared" si="2"/>
+        <f>SUM(AG177, AH177)</f>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI178">
-        <f t="shared" si="2"/>
+        <f>SUM(AG178, AH178)</f>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI179">
-        <f t="shared" si="2"/>
+        <f>SUM(AG179, AH179)</f>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI180">
-        <f t="shared" si="2"/>
+        <f>SUM(AG180, AH180)</f>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI181">
-        <f t="shared" si="2"/>
+        <f>SUM(AG181, AH181)</f>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI182">
-        <f t="shared" si="2"/>
+        <f>SUM(AG182, AH182)</f>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI183">
-        <f t="shared" si="2"/>
+        <f>SUM(AG183, AH183)</f>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI184">
-        <f t="shared" si="2"/>
+        <f>SUM(AG184, AH184)</f>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI185">
-        <f t="shared" si="2"/>
+        <f>SUM(AG185, AH185)</f>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI186">
-        <f t="shared" si="2"/>
+        <f>SUM(AG186, AH186)</f>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI187">
-        <f t="shared" si="2"/>
+        <f>SUM(AG187, AH187)</f>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI188">
-        <f t="shared" si="2"/>
+        <f>SUM(AG188, AH188)</f>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI189">
-        <f t="shared" si="2"/>
+        <f>SUM(AG189, AH189)</f>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI190">
-        <f t="shared" si="2"/>
+        <f>SUM(AG190, AH190)</f>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI191">
-        <f t="shared" si="2"/>
+        <f>SUM(AG191, AH191)</f>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI192">
-        <f t="shared" si="2"/>
+        <f>SUM(AG192, AH192)</f>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI193">
-        <f t="shared" si="2"/>
+        <f>SUM(AG193, AH193)</f>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI194">
-        <f t="shared" ref="AI194:AI257" si="3">SUM(AG194, AH194)</f>
+        <f>SUM(AG194, AH194)</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI195">
-        <f t="shared" si="3"/>
+        <f>SUM(AG195, AH195)</f>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI196">
-        <f t="shared" si="3"/>
+        <f>SUM(AG196, AH196)</f>
         <v>0</v>
       </c>
     </row>
     <row r="197" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI197">
-        <f t="shared" si="3"/>
+        <f>SUM(AG197, AH197)</f>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI198">
-        <f t="shared" si="3"/>
+        <f>SUM(AG198, AH198)</f>
         <v>0</v>
       </c>
     </row>
     <row r="199" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI199">
-        <f t="shared" si="3"/>
+        <f>SUM(AG199, AH199)</f>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI200">
-        <f t="shared" si="3"/>
+        <f>SUM(AG200, AH200)</f>
         <v>0</v>
       </c>
     </row>
     <row r="201" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI201">
-        <f t="shared" si="3"/>
+        <f>SUM(AG201, AH201)</f>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI202">
-        <f t="shared" si="3"/>
+        <f>SUM(AG202, AH202)</f>
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI203">
-        <f t="shared" si="3"/>
+        <f>SUM(AG203, AH203)</f>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI204">
-        <f t="shared" si="3"/>
+        <f>SUM(AG204, AH204)</f>
         <v>0</v>
       </c>
     </row>
     <row r="205" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI205">
-        <f t="shared" si="3"/>
+        <f>SUM(AG205, AH205)</f>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI206">
-        <f t="shared" si="3"/>
+        <f>SUM(AG206, AH206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="207" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI207">
-        <f t="shared" si="3"/>
+        <f>SUM(AG207, AH207)</f>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI208">
-        <f t="shared" si="3"/>
+        <f>SUM(AG208, AH208)</f>
         <v>0</v>
       </c>
     </row>
     <row r="209" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI209">
-        <f t="shared" si="3"/>
+        <f>SUM(AG209, AH209)</f>
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI210">
-        <f t="shared" si="3"/>
+        <f>SUM(AG210, AH210)</f>
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI211">
-        <f t="shared" si="3"/>
+        <f>SUM(AG211, AH211)</f>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI212">
-        <f t="shared" si="3"/>
+        <f>SUM(AG212, AH212)</f>
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI213">
-        <f t="shared" si="3"/>
+        <f>SUM(AG213, AH213)</f>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI214">
-        <f t="shared" si="3"/>
+        <f>SUM(AG214, AH214)</f>
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI215">
-        <f t="shared" si="3"/>
+        <f>SUM(AG215, AH215)</f>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI216">
-        <f t="shared" si="3"/>
+        <f>SUM(AG216, AH216)</f>
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI217">
-        <f t="shared" si="3"/>
+        <f>SUM(AG217, AH217)</f>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI218">
-        <f t="shared" si="3"/>
+        <f>SUM(AG218, AH218)</f>
         <v>0</v>
       </c>
     </row>
     <row r="219" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI219">
-        <f t="shared" si="3"/>
+        <f>SUM(AG219, AH219)</f>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI220">
-        <f t="shared" si="3"/>
+        <f>SUM(AG220, AH220)</f>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI221">
-        <f t="shared" si="3"/>
+        <f>SUM(AG221, AH221)</f>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI222">
-        <f t="shared" si="3"/>
+        <f>SUM(AG222, AH222)</f>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI223">
-        <f t="shared" si="3"/>
+        <f>SUM(AG223, AH223)</f>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI224">
-        <f t="shared" si="3"/>
+        <f>SUM(AG224, AH224)</f>
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI225">
-        <f t="shared" si="3"/>
+        <f>SUM(AG225, AH225)</f>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI226">
-        <f t="shared" si="3"/>
+        <f>SUM(AG226, AH226)</f>
         <v>0</v>
       </c>
     </row>
     <row r="227" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI227">
-        <f t="shared" si="3"/>
+        <f>SUM(AG227, AH227)</f>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI228">
-        <f t="shared" si="3"/>
+        <f>SUM(AG228, AH228)</f>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI229">
-        <f t="shared" si="3"/>
+        <f>SUM(AG229, AH229)</f>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI230">
-        <f t="shared" si="3"/>
+        <f>SUM(AG230, AH230)</f>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI231">
-        <f t="shared" si="3"/>
+        <f>SUM(AG231, AH231)</f>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI232">
-        <f t="shared" si="3"/>
+        <f>SUM(AG232, AH232)</f>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI233">
-        <f t="shared" si="3"/>
+        <f>SUM(AG233, AH233)</f>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI234">
-        <f t="shared" si="3"/>
+        <f>SUM(AG234, AH234)</f>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI235">
-        <f t="shared" si="3"/>
+        <f>SUM(AG235, AH235)</f>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI236">
-        <f t="shared" si="3"/>
+        <f>SUM(AG236, AH236)</f>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI237">
-        <f t="shared" si="3"/>
+        <f>SUM(AG237, AH237)</f>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI238">
-        <f t="shared" si="3"/>
+        <f>SUM(AG238, AH238)</f>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI239">
-        <f t="shared" si="3"/>
+        <f>SUM(AG239, AH239)</f>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI240">
-        <f t="shared" si="3"/>
+        <f>SUM(AG240, AH240)</f>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI241">
-        <f t="shared" si="3"/>
+        <f>SUM(AG241, AH241)</f>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI242">
-        <f t="shared" si="3"/>
+        <f>SUM(AG242, AH242)</f>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI243">
-        <f t="shared" si="3"/>
+        <f>SUM(AG243, AH243)</f>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI244">
-        <f t="shared" si="3"/>
+        <f>SUM(AG244, AH244)</f>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI245">
-        <f t="shared" si="3"/>
+        <f>SUM(AG245, AH245)</f>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI246">
-        <f t="shared" si="3"/>
+        <f>SUM(AG246, AH246)</f>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI247">
-        <f t="shared" si="3"/>
+        <f>SUM(AG247, AH247)</f>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI248">
-        <f t="shared" si="3"/>
+        <f>SUM(AG248, AH248)</f>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI249">
-        <f t="shared" si="3"/>
+        <f>SUM(AG249, AH249)</f>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI250">
-        <f t="shared" si="3"/>
+        <f>SUM(AG250, AH250)</f>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI251">
-        <f t="shared" si="3"/>
+        <f>SUM(AG251, AH251)</f>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI252">
-        <f t="shared" si="3"/>
+        <f>SUM(AG252, AH252)</f>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI253">
-        <f t="shared" si="3"/>
+        <f>SUM(AG253, AH253)</f>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI254">
-        <f t="shared" si="3"/>
+        <f>SUM(AG254, AH254)</f>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI255">
-        <f t="shared" si="3"/>
+        <f>SUM(AG255, AH255)</f>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI256">
-        <f t="shared" si="3"/>
+        <f>SUM(AG256, AH256)</f>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI257">
-        <f t="shared" si="3"/>
+        <f>SUM(AG257, AH257)</f>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI258">
-        <f t="shared" ref="AI258:AI321" si="4">SUM(AG258, AH258)</f>
+        <f>SUM(AG258, AH258)</f>
         <v>0</v>
       </c>
     </row>
     <row r="259" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI259">
-        <f t="shared" si="4"/>
+        <f>SUM(AG259, AH259)</f>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI260">
-        <f t="shared" si="4"/>
+        <f>SUM(AG260, AH260)</f>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI261">
-        <f t="shared" si="4"/>
+        <f>SUM(AG261, AH261)</f>
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI262">
-        <f t="shared" si="4"/>
+        <f>SUM(AG262, AH262)</f>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI263">
-        <f t="shared" si="4"/>
+        <f>SUM(AG263, AH263)</f>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI264">
-        <f t="shared" si="4"/>
+        <f>SUM(AG264, AH264)</f>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI265">
-        <f t="shared" si="4"/>
+        <f>SUM(AG265, AH265)</f>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI266">
-        <f t="shared" si="4"/>
+        <f>SUM(AG266, AH266)</f>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI267">
-        <f t="shared" si="4"/>
+        <f>SUM(AG267, AH267)</f>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI268">
-        <f t="shared" si="4"/>
+        <f>SUM(AG268, AH268)</f>
         <v>0</v>
       </c>
     </row>
     <row r="269" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI269">
-        <f t="shared" si="4"/>
+        <f>SUM(AG269, AH269)</f>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI270">
-        <f t="shared" si="4"/>
+        <f>SUM(AG270, AH270)</f>
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI271">
-        <f t="shared" si="4"/>
+        <f>SUM(AG271, AH271)</f>
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI272">
-        <f t="shared" si="4"/>
+        <f>SUM(AG272, AH272)</f>
         <v>0</v>
       </c>
     </row>
     <row r="273" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI273">
-        <f t="shared" si="4"/>
+        <f>SUM(AG273, AH273)</f>
         <v>0</v>
       </c>
     </row>
     <row r="274" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI274">
-        <f t="shared" si="4"/>
+        <f>SUM(AG274, AH274)</f>
         <v>0</v>
       </c>
     </row>
     <row r="275" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI275">
-        <f t="shared" si="4"/>
+        <f>SUM(AG275, AH275)</f>
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI276">
-        <f t="shared" si="4"/>
+        <f>SUM(AG276, AH276)</f>
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI277">
-        <f t="shared" si="4"/>
+        <f>SUM(AG277, AH277)</f>
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI278">
-        <f t="shared" si="4"/>
+        <f>SUM(AG278, AH278)</f>
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI279">
-        <f t="shared" si="4"/>
+        <f>SUM(AG279, AH279)</f>
         <v>0</v>
       </c>
     </row>
     <row r="280" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI280">
-        <f t="shared" si="4"/>
+        <f>SUM(AG280, AH280)</f>
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI281">
-        <f t="shared" si="4"/>
+        <f>SUM(AG281, AH281)</f>
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI282">
-        <f t="shared" si="4"/>
+        <f>SUM(AG282, AH282)</f>
         <v>0</v>
       </c>
     </row>
     <row r="283" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI283">
-        <f t="shared" si="4"/>
+        <f>SUM(AG283, AH283)</f>
         <v>0</v>
       </c>
     </row>
     <row r="284" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI284">
-        <f t="shared" si="4"/>
+        <f>SUM(AG284, AH284)</f>
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI285">
-        <f t="shared" si="4"/>
+        <f>SUM(AG285, AH285)</f>
         <v>0</v>
       </c>
     </row>
     <row r="286" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI286">
-        <f t="shared" si="4"/>
+        <f>SUM(AG286, AH286)</f>
         <v>0</v>
       </c>
     </row>
     <row r="287" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI287">
-        <f t="shared" si="4"/>
+        <f>SUM(AG287, AH287)</f>
         <v>0</v>
       </c>
     </row>
     <row r="288" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI288">
-        <f t="shared" si="4"/>
+        <f>SUM(AG288, AH288)</f>
         <v>0</v>
       </c>
     </row>
     <row r="289" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI289">
-        <f t="shared" si="4"/>
+        <f>SUM(AG289, AH289)</f>
         <v>0</v>
       </c>
     </row>
     <row r="290" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI290">
-        <f t="shared" si="4"/>
+        <f>SUM(AG290, AH290)</f>
         <v>0</v>
       </c>
     </row>
     <row r="291" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI291">
-        <f t="shared" si="4"/>
+        <f>SUM(AG291, AH291)</f>
         <v>0</v>
       </c>
     </row>
     <row r="292" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI292">
-        <f t="shared" si="4"/>
+        <f>SUM(AG292, AH292)</f>
         <v>0</v>
       </c>
     </row>
     <row r="293" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI293">
-        <f t="shared" si="4"/>
+        <f>SUM(AG293, AH293)</f>
         <v>0</v>
       </c>
     </row>
     <row r="294" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI294">
-        <f t="shared" si="4"/>
+        <f>SUM(AG294, AH294)</f>
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI295">
-        <f t="shared" si="4"/>
+        <f>SUM(AG295, AH295)</f>
         <v>0</v>
       </c>
     </row>
     <row r="296" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI296">
-        <f t="shared" si="4"/>
+        <f>SUM(AG296, AH296)</f>
         <v>0</v>
       </c>
     </row>
     <row r="297" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI297">
-        <f t="shared" si="4"/>
+        <f>SUM(AG297, AH297)</f>
         <v>0</v>
       </c>
     </row>
     <row r="298" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI298">
-        <f t="shared" si="4"/>
+        <f>SUM(AG298, AH298)</f>
         <v>0</v>
       </c>
     </row>
     <row r="299" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI299">
-        <f t="shared" si="4"/>
+        <f>SUM(AG299, AH299)</f>
         <v>0</v>
       </c>
     </row>
     <row r="300" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI300">
-        <f t="shared" si="4"/>
+        <f>SUM(AG300, AH300)</f>
         <v>0</v>
       </c>
     </row>
     <row r="301" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI301">
-        <f t="shared" si="4"/>
+        <f>SUM(AG301, AH301)</f>
         <v>0</v>
       </c>
     </row>
     <row r="302" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI302">
-        <f t="shared" si="4"/>
+        <f>SUM(AG302, AH302)</f>
         <v>0</v>
       </c>
     </row>
     <row r="303" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI303">
-        <f t="shared" si="4"/>
+        <f>SUM(AG303, AH303)</f>
         <v>0</v>
       </c>
     </row>
     <row r="304" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI304">
-        <f t="shared" si="4"/>
+        <f>SUM(AG304, AH304)</f>
         <v>0</v>
       </c>
     </row>
     <row r="305" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI305">
-        <f t="shared" si="4"/>
+        <f>SUM(AG305, AH305)</f>
         <v>0</v>
       </c>
     </row>
     <row r="306" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI306">
-        <f t="shared" si="4"/>
+        <f>SUM(AG306, AH306)</f>
         <v>0</v>
       </c>
     </row>
     <row r="307" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI307">
-        <f t="shared" si="4"/>
+        <f>SUM(AG307, AH307)</f>
         <v>0</v>
       </c>
     </row>
     <row r="308" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI308">
-        <f t="shared" si="4"/>
+        <f>SUM(AG308, AH308)</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI309">
-        <f t="shared" si="4"/>
+        <f>SUM(AG309, AH309)</f>
         <v>0</v>
       </c>
     </row>
     <row r="310" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI310">
-        <f t="shared" si="4"/>
+        <f>SUM(AG310, AH310)</f>
         <v>0</v>
       </c>
     </row>
     <row r="311" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI311">
-        <f t="shared" si="4"/>
+        <f>SUM(AG311, AH311)</f>
         <v>0</v>
       </c>
     </row>
     <row r="312" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI312">
-        <f t="shared" si="4"/>
+        <f>SUM(AG312, AH312)</f>
         <v>0</v>
       </c>
     </row>
     <row r="313" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI313">
-        <f t="shared" si="4"/>
+        <f>SUM(AG313, AH313)</f>
         <v>0</v>
       </c>
     </row>
     <row r="314" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI314">
-        <f t="shared" si="4"/>
+        <f>SUM(AG314, AH314)</f>
         <v>0</v>
       </c>
     </row>
     <row r="315" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI315">
-        <f t="shared" si="4"/>
+        <f>SUM(AG315, AH315)</f>
         <v>0</v>
       </c>
     </row>
     <row r="316" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI316">
-        <f t="shared" si="4"/>
+        <f>SUM(AG316, AH316)</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI317">
-        <f t="shared" si="4"/>
+        <f>SUM(AG317, AH317)</f>
         <v>0</v>
       </c>
     </row>
     <row r="318" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI318">
-        <f t="shared" si="4"/>
+        <f>SUM(AG318, AH318)</f>
         <v>0</v>
       </c>
     </row>
     <row r="319" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI319">
-        <f t="shared" si="4"/>
+        <f>SUM(AG319, AH319)</f>
         <v>0</v>
       </c>
     </row>
     <row r="320" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI320">
-        <f t="shared" si="4"/>
+        <f>SUM(AG320, AH320)</f>
         <v>0</v>
       </c>
     </row>
     <row r="321" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI321">
-        <f t="shared" si="4"/>
+        <f>SUM(AG321, AH321)</f>
         <v>0</v>
       </c>
     </row>
     <row r="322" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI322">
-        <f t="shared" ref="AI322:AI385" si="5">SUM(AG322, AH322)</f>
+        <f>SUM(AG322, AH322)</f>
         <v>0</v>
       </c>
     </row>
     <row r="323" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI323">
-        <f t="shared" si="5"/>
+        <f>SUM(AG323, AH323)</f>
         <v>0</v>
       </c>
     </row>
     <row r="324" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI324">
-        <f t="shared" si="5"/>
+        <f>SUM(AG324, AH324)</f>
         <v>0</v>
       </c>
     </row>
     <row r="325" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI325">
-        <f t="shared" si="5"/>
+        <f>SUM(AG325, AH325)</f>
         <v>0</v>
       </c>
     </row>
     <row r="326" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI326">
-        <f t="shared" si="5"/>
+        <f>SUM(AG326, AH326)</f>
         <v>0</v>
       </c>
     </row>
     <row r="327" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI327">
-        <f t="shared" si="5"/>
+        <f>SUM(AG327, AH327)</f>
         <v>0</v>
       </c>
     </row>
     <row r="328" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI328">
-        <f t="shared" si="5"/>
+        <f>SUM(AG328, AH328)</f>
         <v>0</v>
       </c>
     </row>
     <row r="329" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI329">
-        <f t="shared" si="5"/>
+        <f>SUM(AG329, AH329)</f>
         <v>0</v>
       </c>
     </row>
     <row r="330" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI330">
-        <f t="shared" si="5"/>
+        <f>SUM(AG330, AH330)</f>
         <v>0</v>
       </c>
     </row>
     <row r="331" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI331">
-        <f t="shared" si="5"/>
+        <f>SUM(AG331, AH331)</f>
         <v>0</v>
       </c>
     </row>
     <row r="332" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI332">
-        <f t="shared" si="5"/>
+        <f>SUM(AG332, AH332)</f>
         <v>0</v>
       </c>
     </row>
     <row r="333" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI333">
-        <f t="shared" si="5"/>
+        <f>SUM(AG333, AH333)</f>
         <v>0</v>
       </c>
     </row>
     <row r="334" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI334">
-        <f t="shared" si="5"/>
+        <f>SUM(AG334, AH334)</f>
         <v>0</v>
       </c>
     </row>
     <row r="335" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI335">
-        <f t="shared" si="5"/>
+        <f>SUM(AG335, AH335)</f>
         <v>0</v>
       </c>
     </row>
     <row r="336" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI336">
-        <f t="shared" si="5"/>
+        <f>SUM(AG336, AH336)</f>
         <v>0</v>
       </c>
     </row>
     <row r="337" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI337">
-        <f t="shared" si="5"/>
+        <f>SUM(AG337, AH337)</f>
         <v>0</v>
       </c>
     </row>
     <row r="338" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI338">
-        <f t="shared" si="5"/>
+        <f>SUM(AG338, AH338)</f>
         <v>0</v>
       </c>
     </row>
     <row r="339" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI339">
-        <f t="shared" si="5"/>
+        <f>SUM(AG339, AH339)</f>
         <v>0</v>
       </c>
     </row>
     <row r="340" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI340">
-        <f t="shared" si="5"/>
+        <f>SUM(AG340, AH340)</f>
         <v>0</v>
       </c>
     </row>
     <row r="341" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI341">
-        <f t="shared" si="5"/>
+        <f>SUM(AG341, AH341)</f>
         <v>0</v>
       </c>
     </row>
     <row r="342" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI342">
-        <f t="shared" si="5"/>
+        <f>SUM(AG342, AH342)</f>
         <v>0</v>
       </c>
     </row>
     <row r="343" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI343">
-        <f t="shared" si="5"/>
+        <f>SUM(AG343, AH343)</f>
         <v>0</v>
       </c>
     </row>
     <row r="344" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI344">
-        <f t="shared" si="5"/>
+        <f>SUM(AG344, AH344)</f>
         <v>0</v>
       </c>
     </row>
     <row r="345" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI345">
-        <f t="shared" si="5"/>
+        <f>SUM(AG345, AH345)</f>
         <v>0</v>
       </c>
     </row>
     <row r="346" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI346">
-        <f t="shared" si="5"/>
+        <f>SUM(AG346, AH346)</f>
         <v>0</v>
       </c>
     </row>
     <row r="347" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI347">
-        <f t="shared" si="5"/>
+        <f>SUM(AG347, AH347)</f>
         <v>0</v>
       </c>
     </row>
     <row r="348" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI348">
-        <f t="shared" si="5"/>
+        <f>SUM(AG348, AH348)</f>
         <v>0</v>
       </c>
     </row>
     <row r="349" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI349">
-        <f t="shared" si="5"/>
+        <f>SUM(AG349, AH349)</f>
         <v>0</v>
       </c>
     </row>
     <row r="350" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI350">
-        <f t="shared" si="5"/>
+        <f>SUM(AG350, AH350)</f>
         <v>0</v>
       </c>
     </row>
     <row r="351" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI351">
-        <f t="shared" si="5"/>
+        <f>SUM(AG351, AH351)</f>
         <v>0</v>
       </c>
     </row>
     <row r="352" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI352">
-        <f t="shared" si="5"/>
+        <f>SUM(AG352, AH352)</f>
         <v>0</v>
       </c>
     </row>
     <row r="353" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI353">
-        <f t="shared" si="5"/>
+        <f>SUM(AG353, AH353)</f>
         <v>0</v>
       </c>
     </row>
     <row r="354" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI354">
-        <f t="shared" si="5"/>
+        <f>SUM(AG354, AH354)</f>
         <v>0</v>
       </c>
     </row>
     <row r="355" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI355">
-        <f t="shared" si="5"/>
+        <f>SUM(AG355, AH355)</f>
         <v>0</v>
       </c>
     </row>
     <row r="356" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI356">
-        <f t="shared" si="5"/>
+        <f>SUM(AG356, AH356)</f>
         <v>0</v>
       </c>
     </row>
     <row r="357" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI357">
-        <f t="shared" si="5"/>
+        <f>SUM(AG357, AH357)</f>
         <v>0</v>
       </c>
     </row>
     <row r="358" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI358">
-        <f t="shared" si="5"/>
+        <f>SUM(AG358, AH358)</f>
         <v>0</v>
       </c>
     </row>
     <row r="359" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI359">
-        <f t="shared" si="5"/>
+        <f>SUM(AG359, AH359)</f>
         <v>0</v>
       </c>
     </row>
     <row r="360" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI360">
-        <f t="shared" si="5"/>
+        <f>SUM(AG360, AH360)</f>
         <v>0</v>
       </c>
     </row>
     <row r="361" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI361">
-        <f t="shared" si="5"/>
+        <f>SUM(AG361, AH361)</f>
         <v>0</v>
       </c>
     </row>
     <row r="362" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI362">
-        <f t="shared" si="5"/>
+        <f>SUM(AG362, AH362)</f>
         <v>0</v>
       </c>
     </row>
     <row r="363" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI363">
-        <f t="shared" si="5"/>
+        <f>SUM(AG363, AH363)</f>
         <v>0</v>
       </c>
     </row>
     <row r="364" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI364">
-        <f t="shared" si="5"/>
+        <f>SUM(AG364, AH364)</f>
         <v>0</v>
       </c>
     </row>
     <row r="365" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI365">
-        <f t="shared" si="5"/>
+        <f>SUM(AG365, AH365)</f>
         <v>0</v>
       </c>
     </row>
     <row r="366" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI366">
-        <f t="shared" si="5"/>
+        <f>SUM(AG366, AH366)</f>
         <v>0</v>
       </c>
     </row>
     <row r="367" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI367">
-        <f t="shared" si="5"/>
+        <f>SUM(AG367, AH367)</f>
         <v>0</v>
       </c>
     </row>
     <row r="368" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI368">
-        <f t="shared" si="5"/>
+        <f>SUM(AG368, AH368)</f>
         <v>0</v>
       </c>
     </row>
     <row r="369" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI369">
-        <f t="shared" si="5"/>
+        <f>SUM(AG369, AH369)</f>
         <v>0</v>
       </c>
     </row>
     <row r="370" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI370">
-        <f t="shared" si="5"/>
+        <f>SUM(AG370, AH370)</f>
         <v>0</v>
       </c>
     </row>
     <row r="371" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI371">
-        <f t="shared" si="5"/>
+        <f>SUM(AG371, AH371)</f>
         <v>0</v>
       </c>
     </row>
     <row r="372" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI372">
-        <f t="shared" si="5"/>
+        <f>SUM(AG372, AH372)</f>
         <v>0</v>
       </c>
     </row>
     <row r="373" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI373">
-        <f t="shared" si="5"/>
+        <f>SUM(AG373, AH373)</f>
         <v>0</v>
       </c>
     </row>
     <row r="374" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI374">
-        <f t="shared" si="5"/>
+        <f>SUM(AG374, AH374)</f>
         <v>0</v>
       </c>
     </row>
     <row r="375" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI375">
-        <f t="shared" si="5"/>
+        <f>SUM(AG375, AH375)</f>
         <v>0</v>
       </c>
     </row>
     <row r="376" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI376">
-        <f t="shared" si="5"/>
+        <f>SUM(AG376, AH376)</f>
         <v>0</v>
       </c>
     </row>
     <row r="377" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI377">
-        <f t="shared" si="5"/>
+        <f>SUM(AG377, AH377)</f>
         <v>0</v>
       </c>
     </row>
     <row r="378" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI378">
-        <f t="shared" si="5"/>
+        <f>SUM(AG378, AH378)</f>
         <v>0</v>
       </c>
     </row>
     <row r="379" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI379">
-        <f t="shared" si="5"/>
+        <f>SUM(AG379, AH379)</f>
         <v>0</v>
       </c>
     </row>
     <row r="380" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI380">
-        <f t="shared" si="5"/>
+        <f>SUM(AG380, AH380)</f>
         <v>0</v>
       </c>
     </row>
     <row r="381" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI381">
-        <f t="shared" si="5"/>
+        <f>SUM(AG381, AH381)</f>
         <v>0</v>
       </c>
     </row>
     <row r="382" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI382">
-        <f t="shared" si="5"/>
+        <f>SUM(AG382, AH382)</f>
         <v>0</v>
       </c>
     </row>
     <row r="383" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI383">
-        <f t="shared" si="5"/>
+        <f>SUM(AG383, AH383)</f>
         <v>0</v>
       </c>
     </row>
     <row r="384" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI384">
-        <f t="shared" si="5"/>
+        <f>SUM(AG384, AH384)</f>
         <v>0</v>
       </c>
     </row>
     <row r="385" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI385">
-        <f t="shared" si="5"/>
+        <f>SUM(AG385, AH385)</f>
         <v>0</v>
       </c>
     </row>
     <row r="386" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI386">
-        <f t="shared" ref="AI386:AI449" si="6">SUM(AG386, AH386)</f>
+        <f>SUM(AG386, AH386)</f>
         <v>0</v>
       </c>
     </row>
     <row r="387" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI387">
-        <f t="shared" si="6"/>
+        <f>SUM(AG387, AH387)</f>
         <v>0</v>
       </c>
     </row>
     <row r="388" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI388">
-        <f t="shared" si="6"/>
+        <f>SUM(AG388, AH388)</f>
         <v>0</v>
       </c>
     </row>
     <row r="389" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI389">
-        <f t="shared" si="6"/>
+        <f>SUM(AG389, AH389)</f>
         <v>0</v>
       </c>
     </row>
     <row r="390" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI390">
-        <f t="shared" si="6"/>
+        <f>SUM(AG390, AH390)</f>
         <v>0</v>
       </c>
     </row>
     <row r="391" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI391">
-        <f t="shared" si="6"/>
+        <f>SUM(AG391, AH391)</f>
         <v>0</v>
       </c>
     </row>
     <row r="392" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI392">
-        <f t="shared" si="6"/>
+        <f>SUM(AG392, AH392)</f>
         <v>0</v>
       </c>
     </row>
     <row r="393" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI393">
-        <f t="shared" si="6"/>
+        <f>SUM(AG393, AH393)</f>
         <v>0</v>
       </c>
     </row>
     <row r="394" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI394">
-        <f t="shared" si="6"/>
+        <f>SUM(AG394, AH394)</f>
         <v>0</v>
       </c>
     </row>
     <row r="395" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI395">
-        <f t="shared" si="6"/>
+        <f>SUM(AG395, AH395)</f>
         <v>0</v>
       </c>
     </row>
     <row r="396" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI396">
-        <f t="shared" si="6"/>
+        <f>SUM(AG396, AH396)</f>
         <v>0</v>
       </c>
     </row>
     <row r="397" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI397">
-        <f t="shared" si="6"/>
+        <f>SUM(AG397, AH397)</f>
         <v>0</v>
       </c>
     </row>
     <row r="398" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI398">
-        <f t="shared" si="6"/>
+        <f>SUM(AG398, AH398)</f>
         <v>0</v>
       </c>
     </row>
     <row r="399" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI399">
-        <f t="shared" si="6"/>
+        <f>SUM(AG399, AH399)</f>
         <v>0</v>
       </c>
     </row>
     <row r="400" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI400">
-        <f t="shared" si="6"/>
+        <f>SUM(AG400, AH400)</f>
         <v>0</v>
       </c>
     </row>
     <row r="401" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI401">
-        <f t="shared" si="6"/>
+        <f>SUM(AG401, AH401)</f>
         <v>0</v>
       </c>
     </row>
     <row r="402" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI402">
-        <f t="shared" si="6"/>
+        <f>SUM(AG402, AH402)</f>
         <v>0</v>
       </c>
     </row>
     <row r="403" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI403">
-        <f t="shared" si="6"/>
+        <f>SUM(AG403, AH403)</f>
         <v>0</v>
       </c>
     </row>
     <row r="404" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI404">
-        <f t="shared" si="6"/>
+        <f>SUM(AG404, AH404)</f>
         <v>0</v>
       </c>
     </row>
     <row r="405" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI405">
-        <f t="shared" si="6"/>
+        <f>SUM(AG405, AH405)</f>
         <v>0</v>
       </c>
     </row>
     <row r="406" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI406">
-        <f t="shared" si="6"/>
+        <f>SUM(AG406, AH406)</f>
         <v>0</v>
       </c>
     </row>
     <row r="407" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI407">
-        <f t="shared" si="6"/>
+        <f>SUM(AG407, AH407)</f>
         <v>0</v>
       </c>
     </row>
     <row r="408" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI408">
-        <f t="shared" si="6"/>
+        <f>SUM(AG408, AH408)</f>
         <v>0</v>
       </c>
     </row>
     <row r="409" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI409">
-        <f t="shared" si="6"/>
+        <f>SUM(AG409, AH409)</f>
         <v>0</v>
       </c>
     </row>
     <row r="410" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI410">
-        <f t="shared" si="6"/>
+        <f>SUM(AG410, AH410)</f>
         <v>0</v>
       </c>
     </row>
     <row r="411" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI411">
-        <f t="shared" si="6"/>
+        <f>SUM(AG411, AH411)</f>
         <v>0</v>
       </c>
     </row>
     <row r="412" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI412">
-        <f t="shared" si="6"/>
+        <f>SUM(AG412, AH412)</f>
         <v>0</v>
       </c>
     </row>
     <row r="413" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI413">
-        <f t="shared" si="6"/>
+        <f>SUM(AG413, AH413)</f>
         <v>0</v>
       </c>
     </row>
     <row r="414" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI414">
-        <f t="shared" si="6"/>
+        <f>SUM(AG414, AH414)</f>
         <v>0</v>
       </c>
     </row>
     <row r="415" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI415">
-        <f t="shared" si="6"/>
+        <f>SUM(AG415, AH415)</f>
         <v>0</v>
       </c>
     </row>
     <row r="416" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI416">
-        <f t="shared" si="6"/>
+        <f>SUM(AG416, AH416)</f>
         <v>0</v>
       </c>
     </row>
     <row r="417" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI417">
-        <f t="shared" si="6"/>
+        <f>SUM(AG417, AH417)</f>
         <v>0</v>
       </c>
     </row>
     <row r="418" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI418">
-        <f t="shared" si="6"/>
+        <f>SUM(AG418, AH418)</f>
         <v>0</v>
       </c>
     </row>
     <row r="419" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI419">
-        <f t="shared" si="6"/>
+        <f>SUM(AG419, AH419)</f>
         <v>0</v>
       </c>
     </row>
     <row r="420" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI420">
-        <f t="shared" si="6"/>
+        <f>SUM(AG420, AH420)</f>
         <v>0</v>
       </c>
     </row>
     <row r="421" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI421">
-        <f t="shared" si="6"/>
+        <f>SUM(AG421, AH421)</f>
         <v>0</v>
       </c>
     </row>
     <row r="422" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI422">
-        <f t="shared" si="6"/>
+        <f>SUM(AG422, AH422)</f>
         <v>0</v>
       </c>
     </row>
     <row r="423" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI423">
-        <f t="shared" si="6"/>
+        <f>SUM(AG423, AH423)</f>
         <v>0</v>
       </c>
     </row>
     <row r="424" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI424">
-        <f t="shared" si="6"/>
+        <f>SUM(AG424, AH424)</f>
         <v>0</v>
       </c>
     </row>
     <row r="425" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI425">
-        <f t="shared" si="6"/>
+        <f>SUM(AG425, AH425)</f>
         <v>0</v>
       </c>
     </row>
     <row r="426" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI426">
-        <f t="shared" si="6"/>
+        <f>SUM(AG426, AH426)</f>
         <v>0</v>
       </c>
     </row>
     <row r="427" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI427">
-        <f t="shared" si="6"/>
+        <f>SUM(AG427, AH427)</f>
         <v>0</v>
       </c>
     </row>
     <row r="428" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI428">
-        <f t="shared" si="6"/>
+        <f>SUM(AG428, AH428)</f>
         <v>0</v>
       </c>
     </row>
     <row r="429" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI429">
-        <f t="shared" si="6"/>
+        <f>SUM(AG429, AH429)</f>
         <v>0</v>
       </c>
     </row>
     <row r="430" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI430">
-        <f t="shared" si="6"/>
+        <f>SUM(AG430, AH430)</f>
         <v>0</v>
       </c>
     </row>
     <row r="431" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI431">
-        <f t="shared" si="6"/>
+        <f>SUM(AG431, AH431)</f>
         <v>0</v>
       </c>
     </row>
     <row r="432" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI432">
-        <f t="shared" si="6"/>
+        <f>SUM(AG432, AH432)</f>
         <v>0</v>
       </c>
     </row>
     <row r="433" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI433">
-        <f t="shared" si="6"/>
+        <f>SUM(AG433, AH433)</f>
         <v>0</v>
       </c>
     </row>
     <row r="434" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI434">
-        <f t="shared" si="6"/>
+        <f>SUM(AG434, AH434)</f>
         <v>0</v>
       </c>
     </row>
     <row r="435" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI435">
-        <f t="shared" si="6"/>
+        <f>SUM(AG435, AH435)</f>
         <v>0</v>
       </c>
     </row>
     <row r="436" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI436">
-        <f t="shared" si="6"/>
+        <f>SUM(AG436, AH436)</f>
         <v>0</v>
       </c>
     </row>
     <row r="437" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI437">
-        <f t="shared" si="6"/>
+        <f>SUM(AG437, AH437)</f>
         <v>0</v>
       </c>
     </row>
     <row r="438" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI438">
-        <f t="shared" si="6"/>
+        <f>SUM(AG438, AH438)</f>
         <v>0</v>
       </c>
     </row>
     <row r="439" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI439">
-        <f t="shared" si="6"/>
+        <f>SUM(AG439, AH439)</f>
         <v>0</v>
       </c>
     </row>
     <row r="440" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI440">
-        <f t="shared" si="6"/>
+        <f>SUM(AG440, AH440)</f>
         <v>0</v>
       </c>
     </row>
     <row r="441" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI441">
-        <f t="shared" si="6"/>
+        <f>SUM(AG441, AH441)</f>
         <v>0</v>
       </c>
     </row>
     <row r="442" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI442">
-        <f t="shared" si="6"/>
+        <f>SUM(AG442, AH442)</f>
         <v>0</v>
       </c>
     </row>
     <row r="443" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI443">
-        <f t="shared" si="6"/>
+        <f>SUM(AG443, AH443)</f>
         <v>0</v>
       </c>
     </row>
     <row r="444" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI444">
-        <f t="shared" si="6"/>
+        <f>SUM(AG444, AH444)</f>
         <v>0</v>
       </c>
     </row>
     <row r="445" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI445">
-        <f t="shared" si="6"/>
+        <f>SUM(AG445, AH445)</f>
         <v>0</v>
       </c>
     </row>
     <row r="446" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI446">
-        <f t="shared" si="6"/>
+        <f>SUM(AG446, AH446)</f>
         <v>0</v>
       </c>
     </row>
     <row r="447" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI447">
-        <f t="shared" si="6"/>
+        <f>SUM(AG447, AH447)</f>
         <v>0</v>
       </c>
     </row>
     <row r="448" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI448">
-        <f t="shared" si="6"/>
+        <f>SUM(AG448, AH448)</f>
         <v>0</v>
       </c>
     </row>
     <row r="449" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI449">
-        <f t="shared" si="6"/>
+        <f>SUM(AG449, AH449)</f>
         <v>0</v>
       </c>
     </row>
     <row r="450" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI450">
-        <f t="shared" ref="AI450:AI513" si="7">SUM(AG450, AH450)</f>
+        <f>SUM(AG450, AH450)</f>
         <v>0</v>
       </c>
     </row>
     <row r="451" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI451">
-        <f t="shared" si="7"/>
+        <f>SUM(AG451, AH451)</f>
         <v>0</v>
       </c>
     </row>
     <row r="452" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI452">
-        <f t="shared" si="7"/>
+        <f>SUM(AG452, AH452)</f>
         <v>0</v>
       </c>
     </row>
     <row r="453" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI453">
-        <f t="shared" si="7"/>
+        <f>SUM(AG453, AH453)</f>
         <v>0</v>
       </c>
     </row>
     <row r="454" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI454">
-        <f t="shared" si="7"/>
+        <f>SUM(AG454, AH454)</f>
         <v>0</v>
       </c>
     </row>
     <row r="455" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI455">
-        <f t="shared" si="7"/>
+        <f>SUM(AG455, AH455)</f>
         <v>0</v>
       </c>
     </row>
     <row r="456" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI456">
-        <f t="shared" si="7"/>
+        <f>SUM(AG456, AH456)</f>
         <v>0</v>
       </c>
     </row>
     <row r="457" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI457">
-        <f t="shared" si="7"/>
+        <f>SUM(AG457, AH457)</f>
         <v>0</v>
       </c>
     </row>
     <row r="458" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI458">
-        <f t="shared" si="7"/>
+        <f>SUM(AG458, AH458)</f>
         <v>0</v>
       </c>
     </row>
     <row r="459" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI459">
-        <f t="shared" si="7"/>
+        <f>SUM(AG459, AH459)</f>
         <v>0</v>
       </c>
     </row>
     <row r="460" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI460">
-        <f t="shared" si="7"/>
+        <f>SUM(AG460, AH460)</f>
         <v>0</v>
       </c>
     </row>
     <row r="461" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI461">
-        <f t="shared" si="7"/>
+        <f>SUM(AG461, AH461)</f>
         <v>0</v>
       </c>
     </row>
     <row r="462" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI462">
-        <f t="shared" si="7"/>
+        <f>SUM(AG462, AH462)</f>
         <v>0</v>
       </c>
     </row>
     <row r="463" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI463">
-        <f t="shared" si="7"/>
+        <f>SUM(AG463, AH463)</f>
         <v>0</v>
       </c>
     </row>
     <row r="464" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI464">
-        <f t="shared" si="7"/>
+        <f>SUM(AG464, AH464)</f>
         <v>0</v>
       </c>
     </row>
     <row r="465" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI465">
-        <f t="shared" si="7"/>
+        <f>SUM(AG465, AH465)</f>
         <v>0</v>
       </c>
     </row>
     <row r="466" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI466">
-        <f t="shared" si="7"/>
+        <f>SUM(AG466, AH466)</f>
         <v>0</v>
       </c>
     </row>
     <row r="467" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI467">
-        <f t="shared" si="7"/>
+        <f>SUM(AG467, AH467)</f>
         <v>0</v>
       </c>
     </row>
     <row r="468" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI468">
-        <f t="shared" si="7"/>
+        <f>SUM(AG468, AH468)</f>
         <v>0</v>
       </c>
     </row>
     <row r="469" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI469">
-        <f t="shared" si="7"/>
+        <f>SUM(AG469, AH469)</f>
         <v>0</v>
       </c>
     </row>
     <row r="470" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI470">
-        <f t="shared" si="7"/>
+        <f>SUM(AG470, AH470)</f>
         <v>0</v>
       </c>
     </row>
     <row r="471" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI471">
-        <f t="shared" si="7"/>
+        <f>SUM(AG471, AH471)</f>
         <v>0</v>
       </c>
     </row>
     <row r="472" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI472">
-        <f t="shared" si="7"/>
+        <f>SUM(AG472, AH472)</f>
         <v>0</v>
       </c>
     </row>
     <row r="473" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI473">
-        <f t="shared" si="7"/>
+        <f>SUM(AG473, AH473)</f>
         <v>0</v>
       </c>
     </row>
     <row r="474" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI474">
-        <f t="shared" si="7"/>
+        <f>SUM(AG474, AH474)</f>
         <v>0</v>
       </c>
     </row>
     <row r="475" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI475">
-        <f t="shared" si="7"/>
+        <f>SUM(AG475, AH475)</f>
         <v>0</v>
       </c>
     </row>
     <row r="476" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI476">
-        <f t="shared" si="7"/>
+        <f>SUM(AG476, AH476)</f>
         <v>0</v>
       </c>
     </row>
     <row r="477" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI477">
-        <f t="shared" si="7"/>
+        <f>SUM(AG477, AH477)</f>
         <v>0</v>
       </c>
     </row>
     <row r="478" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI478">
-        <f t="shared" si="7"/>
+        <f>SUM(AG478, AH478)</f>
         <v>0</v>
       </c>
     </row>
     <row r="479" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI479">
-        <f t="shared" si="7"/>
+        <f>SUM(AG479, AH479)</f>
         <v>0</v>
       </c>
     </row>
     <row r="480" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI480">
-        <f t="shared" si="7"/>
+        <f>SUM(AG480, AH480)</f>
         <v>0</v>
       </c>
     </row>
     <row r="481" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI481">
-        <f t="shared" si="7"/>
+        <f>SUM(AG481, AH481)</f>
         <v>0</v>
       </c>
     </row>
     <row r="482" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI482">
-        <f t="shared" si="7"/>
+        <f>SUM(AG482, AH482)</f>
         <v>0</v>
       </c>
     </row>
     <row r="483" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI483">
-        <f t="shared" si="7"/>
+        <f>SUM(AG483, AH483)</f>
         <v>0</v>
       </c>
     </row>
     <row r="484" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI484">
-        <f t="shared" si="7"/>
+        <f>SUM(AG484, AH484)</f>
         <v>0</v>
       </c>
     </row>
     <row r="485" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI485">
-        <f t="shared" si="7"/>
+        <f>SUM(AG485, AH485)</f>
         <v>0</v>
       </c>
     </row>
     <row r="486" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI486">
-        <f t="shared" si="7"/>
+        <f>SUM(AG486, AH486)</f>
         <v>0</v>
       </c>
     </row>
     <row r="487" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI487">
-        <f t="shared" si="7"/>
+        <f>SUM(AG487, AH487)</f>
         <v>0</v>
       </c>
     </row>
     <row r="488" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI488">
-        <f t="shared" si="7"/>
+        <f>SUM(AG488, AH488)</f>
         <v>0</v>
       </c>
     </row>
     <row r="489" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI489">
-        <f t="shared" si="7"/>
+        <f>SUM(AG489, AH489)</f>
         <v>0</v>
       </c>
     </row>
     <row r="490" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI490">
-        <f t="shared" si="7"/>
+        <f>SUM(AG490, AH490)</f>
         <v>0</v>
       </c>
     </row>
     <row r="491" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI491">
-        <f t="shared" si="7"/>
+        <f>SUM(AG491, AH491)</f>
         <v>0</v>
       </c>
     </row>
     <row r="492" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI492">
-        <f t="shared" si="7"/>
+        <f>SUM(AG492, AH492)</f>
         <v>0</v>
       </c>
     </row>
     <row r="493" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI493">
-        <f t="shared" si="7"/>
+        <f>SUM(AG493, AH493)</f>
         <v>0</v>
       </c>
     </row>
     <row r="494" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI494">
-        <f t="shared" si="7"/>
+        <f>SUM(AG494, AH494)</f>
         <v>0</v>
       </c>
     </row>
     <row r="495" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI495">
-        <f t="shared" si="7"/>
+        <f>SUM(AG495, AH495)</f>
         <v>0</v>
       </c>
     </row>
     <row r="496" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI496">
-        <f t="shared" si="7"/>
+        <f>SUM(AG496, AH496)</f>
         <v>0</v>
       </c>
     </row>
     <row r="497" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI497">
-        <f t="shared" si="7"/>
+        <f>SUM(AG497, AH497)</f>
         <v>0</v>
       </c>
     </row>
     <row r="498" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI498">
-        <f t="shared" si="7"/>
+        <f>SUM(AG498, AH498)</f>
         <v>0</v>
       </c>
     </row>
     <row r="499" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI499">
-        <f t="shared" si="7"/>
+        <f>SUM(AG499, AH499)</f>
         <v>0</v>
       </c>
     </row>
     <row r="500" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI500">
-        <f t="shared" si="7"/>
+        <f>SUM(AG500, AH500)</f>
         <v>0</v>
       </c>
     </row>
     <row r="501" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI501">
-        <f t="shared" si="7"/>
+        <f>SUM(AG501, AH501)</f>
         <v>0</v>
       </c>
     </row>
     <row r="502" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI502">
-        <f t="shared" si="7"/>
+        <f>SUM(AG502, AH502)</f>
         <v>0</v>
       </c>
     </row>
     <row r="503" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI503">
-        <f t="shared" si="7"/>
+        <f>SUM(AG503, AH503)</f>
         <v>0</v>
       </c>
     </row>
     <row r="504" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI504">
-        <f t="shared" si="7"/>
+        <f>SUM(AG504, AH504)</f>
         <v>0</v>
       </c>
     </row>
     <row r="505" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI505">
-        <f t="shared" si="7"/>
+        <f>SUM(AG505, AH505)</f>
         <v>0</v>
       </c>
     </row>
     <row r="506" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI506">
-        <f t="shared" si="7"/>
+        <f>SUM(AG506, AH506)</f>
         <v>0</v>
       </c>
     </row>
     <row r="507" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI507">
-        <f t="shared" si="7"/>
+        <f>SUM(AG507, AH507)</f>
         <v>0</v>
       </c>
     </row>
     <row r="508" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI508">
-        <f t="shared" si="7"/>
+        <f>SUM(AG508, AH508)</f>
         <v>0</v>
       </c>
     </row>
     <row r="509" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI509">
-        <f t="shared" si="7"/>
+        <f>SUM(AG509, AH509)</f>
         <v>0</v>
       </c>
     </row>
     <row r="510" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI510">
-        <f t="shared" si="7"/>
+        <f>SUM(AG510, AH510)</f>
         <v>0</v>
       </c>
     </row>
     <row r="511" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI511">
-        <f t="shared" si="7"/>
+        <f>SUM(AG511, AH511)</f>
         <v>0</v>
       </c>
     </row>
     <row r="512" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI512">
-        <f t="shared" si="7"/>
+        <f>SUM(AG512, AH512)</f>
         <v>0</v>
       </c>
     </row>
     <row r="513" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI513">
-        <f t="shared" si="7"/>
+        <f>SUM(AG513, AH513)</f>
         <v>0</v>
       </c>
     </row>
     <row r="514" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI514">
-        <f t="shared" ref="AI514:AI577" si="8">SUM(AG514, AH514)</f>
+        <f>SUM(AG514, AH514)</f>
         <v>0</v>
       </c>
     </row>
     <row r="515" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI515">
-        <f t="shared" si="8"/>
+        <f>SUM(AG515, AH515)</f>
         <v>0</v>
       </c>
     </row>
     <row r="516" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI516">
-        <f t="shared" si="8"/>
+        <f>SUM(AG516, AH516)</f>
         <v>0</v>
       </c>
     </row>
     <row r="517" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI517">
-        <f t="shared" si="8"/>
+        <f>SUM(AG517, AH517)</f>
         <v>0</v>
       </c>
     </row>
     <row r="518" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI518">
-        <f t="shared" si="8"/>
+        <f>SUM(AG518, AH518)</f>
         <v>0</v>
       </c>
     </row>
     <row r="519" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI519">
-        <f t="shared" si="8"/>
+        <f>SUM(AG519, AH519)</f>
         <v>0</v>
       </c>
     </row>
     <row r="520" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI520">
-        <f t="shared" si="8"/>
+        <f>SUM(AG520, AH520)</f>
         <v>0</v>
       </c>
     </row>
     <row r="521" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI521">
-        <f t="shared" si="8"/>
+        <f>SUM(AG521, AH521)</f>
         <v>0</v>
       </c>
     </row>
     <row r="522" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI522">
-        <f t="shared" si="8"/>
+        <f>SUM(AG522, AH522)</f>
         <v>0</v>
       </c>
     </row>
     <row r="523" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI523">
-        <f t="shared" si="8"/>
+        <f>SUM(AG523, AH523)</f>
         <v>0</v>
       </c>
     </row>
     <row r="524" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI524">
-        <f t="shared" si="8"/>
+        <f>SUM(AG524, AH524)</f>
         <v>0</v>
       </c>
     </row>
     <row r="525" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI525">
-        <f t="shared" si="8"/>
+        <f>SUM(AG525, AH525)</f>
         <v>0</v>
       </c>
     </row>
     <row r="526" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI526">
-        <f t="shared" si="8"/>
+        <f>SUM(AG526, AH526)</f>
         <v>0</v>
       </c>
     </row>
     <row r="527" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI527">
-        <f t="shared" si="8"/>
+        <f>SUM(AG527, AH527)</f>
         <v>0</v>
       </c>
     </row>
     <row r="528" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI528">
-        <f t="shared" si="8"/>
+        <f>SUM(AG528, AH528)</f>
         <v>0</v>
       </c>
     </row>
     <row r="529" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI529">
-        <f t="shared" si="8"/>
+        <f>SUM(AG529, AH529)</f>
         <v>0</v>
       </c>
     </row>
     <row r="530" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI530">
-        <f t="shared" si="8"/>
+        <f>SUM(AG530, AH530)</f>
         <v>0</v>
       </c>
     </row>
     <row r="531" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI531">
-        <f t="shared" si="8"/>
+        <f>SUM(AG531, AH531)</f>
         <v>0</v>
       </c>
     </row>
     <row r="532" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI532">
-        <f t="shared" si="8"/>
+        <f>SUM(AG532, AH532)</f>
         <v>0</v>
       </c>
     </row>
     <row r="533" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI533">
-        <f t="shared" si="8"/>
+        <f>SUM(AG533, AH533)</f>
         <v>0</v>
       </c>
     </row>
     <row r="534" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI534">
-        <f t="shared" si="8"/>
+        <f>SUM(AG534, AH534)</f>
         <v>0</v>
       </c>
     </row>
     <row r="535" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI535">
-        <f t="shared" si="8"/>
+        <f>SUM(AG535, AH535)</f>
         <v>0</v>
       </c>
     </row>
     <row r="536" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI536">
-        <f t="shared" si="8"/>
+        <f>SUM(AG536, AH536)</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI537">
-        <f t="shared" si="8"/>
+        <f>SUM(AG537, AH537)</f>
         <v>0</v>
       </c>
     </row>
     <row r="538" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI538">
-        <f t="shared" si="8"/>
+        <f>SUM(AG538, AH538)</f>
         <v>0</v>
       </c>
     </row>
     <row r="539" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI539">
-        <f t="shared" si="8"/>
+        <f>SUM(AG539, AH539)</f>
         <v>0</v>
       </c>
     </row>
     <row r="540" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI540">
-        <f t="shared" si="8"/>
+        <f>SUM(AG540, AH540)</f>
         <v>0</v>
       </c>
     </row>
     <row r="541" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI541">
-        <f t="shared" si="8"/>
+        <f>SUM(AG541, AH541)</f>
         <v>0</v>
       </c>
     </row>
     <row r="542" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI542">
-        <f t="shared" si="8"/>
+        <f>SUM(AG542, AH542)</f>
         <v>0</v>
       </c>
     </row>
     <row r="543" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI543">
-        <f t="shared" si="8"/>
+        <f>SUM(AG543, AH543)</f>
         <v>0</v>
       </c>
     </row>
     <row r="544" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI544">
-        <f t="shared" si="8"/>
+        <f>SUM(AG544, AH544)</f>
         <v>0</v>
       </c>
     </row>
     <row r="545" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI545">
-        <f t="shared" si="8"/>
+        <f>SUM(AG545, AH545)</f>
         <v>0</v>
       </c>
     </row>
     <row r="546" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI546">
-        <f t="shared" si="8"/>
+        <f>SUM(AG546, AH546)</f>
         <v>0</v>
       </c>
     </row>
     <row r="547" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI547">
-        <f t="shared" si="8"/>
+        <f>SUM(AG547, AH547)</f>
         <v>0</v>
       </c>
     </row>
     <row r="548" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI548">
-        <f t="shared" si="8"/>
+        <f>SUM(AG548, AH548)</f>
         <v>0</v>
       </c>
     </row>
     <row r="549" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI549">
-        <f t="shared" si="8"/>
+        <f>SUM(AG549, AH549)</f>
         <v>0</v>
       </c>
     </row>
     <row r="550" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI550">
-        <f t="shared" si="8"/>
+        <f>SUM(AG550, AH550)</f>
         <v>0</v>
       </c>
     </row>
     <row r="551" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI551">
-        <f t="shared" si="8"/>
+        <f>SUM(AG551, AH551)</f>
         <v>0</v>
       </c>
     </row>
     <row r="552" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI552">
-        <f t="shared" si="8"/>
+        <f>SUM(AG552, AH552)</f>
         <v>0</v>
       </c>
     </row>
     <row r="553" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI553">
-        <f t="shared" si="8"/>
+        <f>SUM(AG553, AH553)</f>
         <v>0</v>
       </c>
     </row>
     <row r="554" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI554">
-        <f t="shared" si="8"/>
+        <f>SUM(AG554, AH554)</f>
         <v>0</v>
       </c>
     </row>
     <row r="555" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI555">
-        <f t="shared" si="8"/>
+        <f>SUM(AG555, AH555)</f>
         <v>0</v>
       </c>
     </row>
     <row r="556" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI556">
-        <f t="shared" si="8"/>
+        <f>SUM(AG556, AH556)</f>
         <v>0</v>
       </c>
     </row>
     <row r="557" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI557">
-        <f t="shared" si="8"/>
+        <f>SUM(AG557, AH557)</f>
         <v>0</v>
       </c>
     </row>
     <row r="558" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI558">
-        <f t="shared" si="8"/>
+        <f>SUM(AG558, AH558)</f>
         <v>0</v>
       </c>
     </row>
     <row r="559" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI559">
-        <f t="shared" si="8"/>
+        <f>SUM(AG559, AH559)</f>
         <v>0</v>
       </c>
     </row>
     <row r="560" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI560">
-        <f t="shared" si="8"/>
+        <f>SUM(AG560, AH560)</f>
         <v>0</v>
       </c>
     </row>
     <row r="561" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI561">
-        <f t="shared" si="8"/>
+        <f>SUM(AG561, AH561)</f>
         <v>0</v>
       </c>
     </row>
     <row r="562" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI562">
-        <f t="shared" si="8"/>
+        <f>SUM(AG562, AH562)</f>
         <v>0</v>
       </c>
     </row>
     <row r="563" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI563">
-        <f t="shared" si="8"/>
+        <f>SUM(AG563, AH563)</f>
         <v>0</v>
       </c>
     </row>
     <row r="564" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI564">
-        <f t="shared" si="8"/>
+        <f>SUM(AG564, AH564)</f>
         <v>0</v>
       </c>
     </row>
     <row r="565" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI565">
-        <f t="shared" si="8"/>
+        <f>SUM(AG565, AH565)</f>
         <v>0</v>
       </c>
     </row>
     <row r="566" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI566">
-        <f t="shared" si="8"/>
+        <f>SUM(AG566, AH566)</f>
         <v>0</v>
       </c>
     </row>
     <row r="567" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI567">
-        <f t="shared" si="8"/>
+        <f>SUM(AG567, AH567)</f>
         <v>0</v>
       </c>
     </row>
     <row r="568" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI568">
-        <f t="shared" si="8"/>
+        <f>SUM(AG568, AH568)</f>
         <v>0</v>
       </c>
     </row>
     <row r="569" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI569">
-        <f t="shared" si="8"/>
+        <f>SUM(AG569, AH569)</f>
         <v>0</v>
       </c>
     </row>
     <row r="570" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI570">
-        <f t="shared" si="8"/>
+        <f>SUM(AG570, AH570)</f>
         <v>0</v>
       </c>
     </row>
     <row r="571" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI571">
-        <f t="shared" si="8"/>
+        <f>SUM(AG571, AH571)</f>
         <v>0</v>
       </c>
     </row>
     <row r="572" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI572">
-        <f t="shared" si="8"/>
+        <f>SUM(AG572, AH572)</f>
         <v>0</v>
       </c>
     </row>
     <row r="573" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI573">
-        <f t="shared" si="8"/>
+        <f>SUM(AG573, AH573)</f>
         <v>0</v>
       </c>
     </row>
     <row r="574" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI574">
-        <f t="shared" si="8"/>
+        <f>SUM(AG574, AH574)</f>
         <v>0</v>
       </c>
     </row>
     <row r="575" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI575">
-        <f t="shared" si="8"/>
+        <f>SUM(AG575, AH575)</f>
         <v>0</v>
       </c>
     </row>
     <row r="576" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI576">
-        <f t="shared" si="8"/>
+        <f>SUM(AG576, AH576)</f>
         <v>0</v>
       </c>
     </row>
     <row r="577" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI577">
-        <f t="shared" si="8"/>
+        <f>SUM(AG577, AH577)</f>
         <v>0</v>
       </c>
     </row>
     <row r="578" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI578">
-        <f t="shared" ref="AI578:AI641" si="9">SUM(AG578, AH578)</f>
+        <f>SUM(AG578, AH578)</f>
         <v>0</v>
       </c>
     </row>
     <row r="579" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI579">
-        <f t="shared" si="9"/>
+        <f>SUM(AG579, AH579)</f>
         <v>0</v>
       </c>
     </row>
     <row r="580" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI580">
-        <f t="shared" si="9"/>
+        <f>SUM(AG580, AH580)</f>
         <v>0</v>
       </c>
     </row>
     <row r="581" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI581">
-        <f t="shared" si="9"/>
+        <f>SUM(AG581, AH581)</f>
         <v>0</v>
       </c>
     </row>
     <row r="582" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI582">
-        <f t="shared" si="9"/>
+        <f>SUM(AG582, AH582)</f>
         <v>0</v>
       </c>
     </row>
     <row r="583" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI583">
-        <f t="shared" si="9"/>
+        <f>SUM(AG583, AH583)</f>
         <v>0</v>
       </c>
     </row>
     <row r="584" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI584">
-        <f t="shared" si="9"/>
+        <f>SUM(AG584, AH584)</f>
         <v>0</v>
       </c>
     </row>
     <row r="585" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI585">
-        <f t="shared" si="9"/>
+        <f>SUM(AG585, AH585)</f>
         <v>0</v>
       </c>
     </row>
     <row r="586" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI586">
-        <f t="shared" si="9"/>
+        <f>SUM(AG586, AH586)</f>
         <v>0</v>
       </c>
     </row>
     <row r="587" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI587">
-        <f t="shared" si="9"/>
+        <f>SUM(AG587, AH587)</f>
         <v>0</v>
       </c>
     </row>
     <row r="588" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI588">
-        <f t="shared" si="9"/>
+        <f>SUM(AG588, AH588)</f>
         <v>0</v>
       </c>
     </row>
     <row r="589" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI589">
-        <f t="shared" si="9"/>
+        <f>SUM(AG589, AH589)</f>
         <v>0</v>
       </c>
     </row>
     <row r="590" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI590">
-        <f t="shared" si="9"/>
+        <f>SUM(AG590, AH590)</f>
         <v>0</v>
       </c>
     </row>
     <row r="591" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI591">
-        <f t="shared" si="9"/>
+        <f>SUM(AG591, AH591)</f>
         <v>0</v>
       </c>
     </row>
     <row r="592" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI592">
-        <f t="shared" si="9"/>
+        <f>SUM(AG592, AH592)</f>
         <v>0</v>
       </c>
     </row>
     <row r="593" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI593">
-        <f t="shared" si="9"/>
+        <f>SUM(AG593, AH593)</f>
         <v>0</v>
       </c>
     </row>
     <row r="594" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI594">
-        <f t="shared" si="9"/>
+        <f>SUM(AG594, AH594)</f>
         <v>0</v>
       </c>
     </row>
     <row r="595" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI595">
-        <f t="shared" si="9"/>
+        <f>SUM(AG595, AH595)</f>
         <v>0</v>
       </c>
     </row>
     <row r="596" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI596">
-        <f t="shared" si="9"/>
+        <f>SUM(AG596, AH596)</f>
         <v>0</v>
       </c>
     </row>
     <row r="597" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI597">
-        <f t="shared" si="9"/>
+        <f>SUM(AG597, AH597)</f>
         <v>0</v>
       </c>
     </row>
     <row r="598" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI598">
-        <f t="shared" si="9"/>
+        <f>SUM(AG598, AH598)</f>
         <v>0</v>
       </c>
     </row>
     <row r="599" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI599">
-        <f t="shared" si="9"/>
+        <f>SUM(AG599, AH599)</f>
         <v>0</v>
       </c>
     </row>
     <row r="600" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI600">
-        <f t="shared" si="9"/>
+        <f>SUM(AG600, AH600)</f>
         <v>0</v>
       </c>
     </row>
     <row r="601" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI601">
-        <f t="shared" si="9"/>
+        <f>SUM(AG601, AH601)</f>
         <v>0</v>
       </c>
     </row>
     <row r="602" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI602">
-        <f t="shared" si="9"/>
+        <f>SUM(AG602, AH602)</f>
         <v>0</v>
       </c>
     </row>
     <row r="603" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI603">
-        <f t="shared" si="9"/>
+        <f>SUM(AG603, AH603)</f>
         <v>0</v>
       </c>
     </row>
     <row r="604" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI604">
-        <f t="shared" si="9"/>
+        <f>SUM(AG604, AH604)</f>
         <v>0</v>
       </c>
     </row>
     <row r="605" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI605">
-        <f t="shared" si="9"/>
+        <f>SUM(AG605, AH605)</f>
         <v>0</v>
       </c>
     </row>
     <row r="606" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI606">
-        <f t="shared" si="9"/>
+        <f>SUM(AG606, AH606)</f>
         <v>0</v>
       </c>
     </row>
     <row r="607" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI607">
-        <f t="shared" si="9"/>
+        <f>SUM(AG607, AH607)</f>
         <v>0</v>
       </c>
     </row>
     <row r="608" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI608">
-        <f t="shared" si="9"/>
+        <f>SUM(AG608, AH608)</f>
         <v>0</v>
       </c>
     </row>
     <row r="609" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI609">
-        <f t="shared" si="9"/>
+        <f>SUM(AG609, AH609)</f>
         <v>0</v>
       </c>
     </row>
     <row r="610" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI610">
-        <f t="shared" si="9"/>
+        <f>SUM(AG610, AH610)</f>
         <v>0</v>
       </c>
     </row>
     <row r="611" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI611">
-        <f t="shared" si="9"/>
+        <f>SUM(AG611, AH611)</f>
         <v>0</v>
       </c>
     </row>
     <row r="612" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI612">
-        <f t="shared" si="9"/>
+        <f>SUM(AG612, AH612)</f>
         <v>0</v>
       </c>
     </row>
     <row r="613" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI613">
-        <f t="shared" si="9"/>
+        <f>SUM(AG613, AH613)</f>
         <v>0</v>
       </c>
     </row>
     <row r="614" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI614">
-        <f t="shared" si="9"/>
+        <f>SUM(AG614, AH614)</f>
         <v>0</v>
       </c>
     </row>
     <row r="615" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI615">
-        <f t="shared" si="9"/>
+        <f>SUM(AG615, AH615)</f>
         <v>0</v>
       </c>
     </row>
     <row r="616" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI616">
-        <f t="shared" si="9"/>
+        <f>SUM(AG616, AH616)</f>
         <v>0</v>
       </c>
     </row>
     <row r="617" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI617">
-        <f t="shared" si="9"/>
+        <f>SUM(AG617, AH617)</f>
         <v>0</v>
       </c>
     </row>
     <row r="618" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI618">
-        <f t="shared" si="9"/>
+        <f>SUM(AG618, AH618)</f>
         <v>0</v>
       </c>
     </row>
     <row r="619" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI619">
-        <f t="shared" si="9"/>
+        <f>SUM(AG619, AH619)</f>
         <v>0</v>
       </c>
     </row>
     <row r="620" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI620">
-        <f t="shared" si="9"/>
+        <f>SUM(AG620, AH620)</f>
         <v>0</v>
       </c>
     </row>
     <row r="621" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI621">
-        <f t="shared" si="9"/>
+        <f>SUM(AG621, AH621)</f>
         <v>0</v>
       </c>
     </row>
     <row r="622" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI622">
-        <f t="shared" si="9"/>
+        <f>SUM(AG622, AH622)</f>
         <v>0</v>
       </c>
     </row>
     <row r="623" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI623">
-        <f t="shared" si="9"/>
+        <f>SUM(AG623, AH623)</f>
         <v>0</v>
       </c>
     </row>
     <row r="624" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI624">
-        <f t="shared" si="9"/>
+        <f>SUM(AG624, AH624)</f>
         <v>0</v>
       </c>
     </row>
     <row r="625" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI625">
-        <f t="shared" si="9"/>
+        <f>SUM(AG625, AH625)</f>
         <v>0</v>
       </c>
     </row>
     <row r="626" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI626">
-        <f t="shared" si="9"/>
+        <f>SUM(AG626, AH626)</f>
         <v>0</v>
       </c>
     </row>
     <row r="627" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI627">
-        <f t="shared" si="9"/>
+        <f>SUM(AG627, AH627)</f>
         <v>0</v>
       </c>
     </row>
     <row r="628" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI628">
-        <f t="shared" si="9"/>
+        <f>SUM(AG628, AH628)</f>
         <v>0</v>
       </c>
     </row>
     <row r="629" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI629">
-        <f t="shared" si="9"/>
+        <f>SUM(AG629, AH629)</f>
         <v>0</v>
       </c>
     </row>
     <row r="630" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI630">
-        <f t="shared" si="9"/>
+        <f>SUM(AG630, AH630)</f>
         <v>0</v>
       </c>
     </row>
     <row r="631" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI631">
-        <f t="shared" si="9"/>
+        <f>SUM(AG631, AH631)</f>
         <v>0</v>
       </c>
     </row>
     <row r="632" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI632">
-        <f t="shared" si="9"/>
+        <f>SUM(AG632, AH632)</f>
         <v>0</v>
       </c>
     </row>
     <row r="633" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI633">
-        <f t="shared" si="9"/>
+        <f>SUM(AG633, AH633)</f>
         <v>0</v>
       </c>
     </row>
     <row r="634" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI634">
-        <f t="shared" si="9"/>
+        <f>SUM(AG634, AH634)</f>
         <v>0</v>
       </c>
     </row>
     <row r="635" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI635">
-        <f t="shared" si="9"/>
+        <f>SUM(AG635, AH635)</f>
         <v>0</v>
       </c>
     </row>
     <row r="636" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI636">
-        <f t="shared" si="9"/>
+        <f>SUM(AG636, AH636)</f>
         <v>0</v>
       </c>
     </row>
     <row r="637" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI637">
-        <f t="shared" si="9"/>
+        <f>SUM(AG637, AH637)</f>
         <v>0</v>
       </c>
     </row>
     <row r="638" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI638">
-        <f t="shared" si="9"/>
+        <f>SUM(AG638, AH638)</f>
         <v>0</v>
       </c>
     </row>
     <row r="639" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI639">
-        <f t="shared" si="9"/>
+        <f>SUM(AG639, AH639)</f>
         <v>0</v>
       </c>
     </row>
     <row r="640" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI640">
-        <f t="shared" si="9"/>
+        <f>SUM(AG640, AH640)</f>
         <v>0</v>
       </c>
     </row>
     <row r="641" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI641">
-        <f t="shared" si="9"/>
+        <f>SUM(AG641, AH641)</f>
         <v>0</v>
       </c>
     </row>
     <row r="642" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI642">
-        <f t="shared" ref="AI642:AI705" si="10">SUM(AG642, AH642)</f>
+        <f>SUM(AG642, AH642)</f>
         <v>0</v>
       </c>
     </row>
     <row r="643" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI643">
-        <f t="shared" si="10"/>
+        <f>SUM(AG643, AH643)</f>
         <v>0</v>
       </c>
     </row>
     <row r="644" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI644">
-        <f t="shared" si="10"/>
+        <f>SUM(AG644, AH644)</f>
         <v>0</v>
       </c>
     </row>
     <row r="645" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI645">
-        <f t="shared" si="10"/>
+        <f>SUM(AG645, AH645)</f>
         <v>0</v>
       </c>
     </row>
     <row r="646" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI646">
-        <f t="shared" si="10"/>
+        <f>SUM(AG646, AH646)</f>
         <v>0</v>
       </c>
     </row>
     <row r="647" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI647">
-        <f t="shared" si="10"/>
+        <f>SUM(AG647, AH647)</f>
         <v>0</v>
       </c>
     </row>
     <row r="648" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI648">
-        <f t="shared" si="10"/>
+        <f>SUM(AG648, AH648)</f>
         <v>0</v>
       </c>
     </row>
     <row r="649" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI649">
-        <f t="shared" si="10"/>
+        <f>SUM(AG649, AH649)</f>
         <v>0</v>
       </c>
     </row>
     <row r="650" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI650">
-        <f t="shared" si="10"/>
+        <f>SUM(AG650, AH650)</f>
         <v>0</v>
       </c>
     </row>
     <row r="651" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI651">
-        <f t="shared" si="10"/>
+        <f>SUM(AG651, AH651)</f>
         <v>0</v>
       </c>
     </row>
     <row r="652" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI652">
-        <f t="shared" si="10"/>
+        <f>SUM(AG652, AH652)</f>
         <v>0</v>
       </c>
     </row>
     <row r="653" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI653">
-        <f t="shared" si="10"/>
+        <f>SUM(AG653, AH653)</f>
         <v>0</v>
       </c>
     </row>
     <row r="654" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI654">
-        <f t="shared" si="10"/>
+        <f>SUM(AG654, AH654)</f>
         <v>0</v>
       </c>
     </row>
     <row r="655" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI655">
-        <f t="shared" si="10"/>
+        <f>SUM(AG655, AH655)</f>
         <v>0</v>
       </c>
     </row>
     <row r="656" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI656">
-        <f t="shared" si="10"/>
+        <f>SUM(AG656, AH656)</f>
         <v>0</v>
       </c>
     </row>
     <row r="657" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI657">
-        <f t="shared" si="10"/>
+        <f>SUM(AG657, AH657)</f>
         <v>0</v>
       </c>
     </row>
     <row r="658" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI658">
-        <f t="shared" si="10"/>
+        <f>SUM(AG658, AH658)</f>
         <v>0</v>
       </c>
     </row>
     <row r="659" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI659">
-        <f t="shared" si="10"/>
+        <f>SUM(AG659, AH659)</f>
         <v>0</v>
       </c>
     </row>
     <row r="660" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI660">
-        <f t="shared" si="10"/>
+        <f>SUM(AG660, AH660)</f>
         <v>0</v>
       </c>
     </row>
     <row r="661" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI661">
-        <f t="shared" si="10"/>
+        <f>SUM(AG661, AH661)</f>
         <v>0</v>
       </c>
     </row>
     <row r="662" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI662">
-        <f t="shared" si="10"/>
+        <f>SUM(AG662, AH662)</f>
         <v>0</v>
       </c>
     </row>
     <row r="663" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI663">
-        <f t="shared" si="10"/>
+        <f>SUM(AG663, AH663)</f>
         <v>0</v>
       </c>
     </row>
     <row r="664" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI664">
-        <f t="shared" si="10"/>
+        <f>SUM(AG664, AH664)</f>
         <v>0</v>
       </c>
     </row>
     <row r="665" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI665">
-        <f t="shared" si="10"/>
+        <f>SUM(AG665, AH665)</f>
         <v>0</v>
       </c>
     </row>
     <row r="666" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI666">
-        <f t="shared" si="10"/>
+        <f>SUM(AG666, AH666)</f>
         <v>0</v>
       </c>
     </row>
     <row r="667" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI667">
-        <f t="shared" si="10"/>
+        <f>SUM(AG667, AH667)</f>
         <v>0</v>
       </c>
     </row>
     <row r="668" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI668">
-        <f t="shared" si="10"/>
+        <f>SUM(AG668, AH668)</f>
         <v>0</v>
       </c>
     </row>
     <row r="669" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI669">
-        <f t="shared" si="10"/>
+        <f>SUM(AG669, AH669)</f>
         <v>0</v>
       </c>
     </row>
     <row r="670" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI670">
-        <f t="shared" si="10"/>
+        <f>SUM(AG670, AH670)</f>
         <v>0</v>
       </c>
     </row>
     <row r="671" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI671">
-        <f t="shared" si="10"/>
+        <f>SUM(AG671, AH671)</f>
         <v>0</v>
       </c>
     </row>
     <row r="672" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI672">
-        <f t="shared" si="10"/>
+        <f>SUM(AG672, AH672)</f>
         <v>0</v>
       </c>
     </row>
     <row r="673" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI673">
-        <f t="shared" si="10"/>
+        <f>SUM(AG673, AH673)</f>
         <v>0</v>
       </c>
     </row>
     <row r="674" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI674">
-        <f t="shared" si="10"/>
+        <f>SUM(AG674, AH674)</f>
         <v>0</v>
       </c>
     </row>
     <row r="675" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI675">
-        <f t="shared" si="10"/>
+        <f>SUM(AG675, AH675)</f>
         <v>0</v>
       </c>
     </row>
     <row r="676" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI676">
-        <f t="shared" si="10"/>
+        <f>SUM(AG676, AH676)</f>
         <v>0</v>
       </c>
     </row>
     <row r="677" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI677">
-        <f t="shared" si="10"/>
+        <f>SUM(AG677, AH677)</f>
         <v>0</v>
       </c>
     </row>
     <row r="678" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI678">
-        <f t="shared" si="10"/>
+        <f>SUM(AG678, AH678)</f>
         <v>0</v>
       </c>
     </row>
     <row r="679" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI679">
-        <f t="shared" si="10"/>
+        <f>SUM(AG679, AH679)</f>
         <v>0</v>
       </c>
     </row>
     <row r="680" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI680">
-        <f t="shared" si="10"/>
+        <f>SUM(AG680, AH680)</f>
         <v>0</v>
       </c>
     </row>
     <row r="681" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI681">
-        <f t="shared" si="10"/>
+        <f>SUM(AG681, AH681)</f>
         <v>0</v>
       </c>
     </row>
     <row r="682" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI682">
-        <f t="shared" si="10"/>
+        <f>SUM(AG682, AH682)</f>
         <v>0</v>
       </c>
     </row>
     <row r="683" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI683">
-        <f t="shared" si="10"/>
+        <f>SUM(AG683, AH683)</f>
         <v>0</v>
       </c>
     </row>
     <row r="684" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI684">
-        <f t="shared" si="10"/>
+        <f>SUM(AG684, AH684)</f>
         <v>0</v>
       </c>
     </row>
     <row r="685" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI685">
-        <f t="shared" si="10"/>
+        <f>SUM(AG685, AH685)</f>
         <v>0</v>
       </c>
     </row>
     <row r="686" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI686">
-        <f t="shared" si="10"/>
+        <f>SUM(AG686, AH686)</f>
         <v>0</v>
       </c>
     </row>
     <row r="687" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI687">
-        <f t="shared" si="10"/>
+        <f>SUM(AG687, AH687)</f>
         <v>0</v>
       </c>
     </row>
     <row r="688" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI688">
-        <f t="shared" si="10"/>
+        <f>SUM(AG688, AH688)</f>
         <v>0</v>
       </c>
     </row>
     <row r="689" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI689">
-        <f t="shared" si="10"/>
+        <f>SUM(AG689, AH689)</f>
         <v>0</v>
       </c>
     </row>
     <row r="690" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI690">
-        <f t="shared" si="10"/>
+        <f>SUM(AG690, AH690)</f>
         <v>0</v>
       </c>
     </row>
     <row r="691" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI691">
-        <f t="shared" si="10"/>
+        <f>SUM(AG691, AH691)</f>
         <v>0</v>
       </c>
     </row>
     <row r="692" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI692">
-        <f t="shared" si="10"/>
+        <f>SUM(AG692, AH692)</f>
         <v>0</v>
       </c>
     </row>
     <row r="693" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI693">
-        <f t="shared" si="10"/>
+        <f>SUM(AG693, AH693)</f>
         <v>0</v>
       </c>
     </row>
     <row r="694" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI694">
-        <f t="shared" si="10"/>
+        <f>SUM(AG694, AH694)</f>
         <v>0</v>
       </c>
     </row>
     <row r="695" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI695">
-        <f t="shared" si="10"/>
+        <f>SUM(AG695, AH695)</f>
         <v>0</v>
       </c>
     </row>
     <row r="696" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI696">
-        <f t="shared" si="10"/>
+        <f>SUM(AG696, AH696)</f>
         <v>0</v>
       </c>
     </row>
     <row r="697" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI697">
-        <f t="shared" si="10"/>
+        <f>SUM(AG697, AH697)</f>
         <v>0</v>
       </c>
     </row>
     <row r="698" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI698">
-        <f t="shared" si="10"/>
+        <f>SUM(AG698, AH698)</f>
         <v>0</v>
       </c>
     </row>
     <row r="699" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI699">
-        <f t="shared" si="10"/>
+        <f>SUM(AG699, AH699)</f>
         <v>0</v>
       </c>
     </row>
     <row r="700" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI700">
-        <f t="shared" si="10"/>
+        <f>SUM(AG700, AH700)</f>
         <v>0</v>
       </c>
     </row>
     <row r="701" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI701">
-        <f t="shared" si="10"/>
+        <f>SUM(AG701, AH701)</f>
         <v>0</v>
       </c>
     </row>
     <row r="702" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI702">
-        <f t="shared" si="10"/>
+        <f>SUM(AG702, AH702)</f>
         <v>0</v>
       </c>
     </row>
     <row r="703" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI703">
-        <f t="shared" si="10"/>
+        <f>SUM(AG703, AH703)</f>
         <v>0</v>
       </c>
     </row>
     <row r="704" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI704">
-        <f t="shared" si="10"/>
+        <f>SUM(AG704, AH704)</f>
         <v>0</v>
       </c>
     </row>
     <row r="705" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI705">
-        <f t="shared" si="10"/>
+        <f>SUM(AG705, AH705)</f>
         <v>0</v>
       </c>
     </row>
     <row r="706" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI706">
-        <f t="shared" ref="AI706:AI769" si="11">SUM(AG706, AH706)</f>
+        <f>SUM(AG706, AH706)</f>
         <v>0</v>
       </c>
     </row>
     <row r="707" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI707">
-        <f t="shared" si="11"/>
+        <f>SUM(AG707, AH707)</f>
         <v>0</v>
       </c>
     </row>
     <row r="708" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI708">
-        <f t="shared" si="11"/>
+        <f>SUM(AG708, AH708)</f>
         <v>0</v>
       </c>
     </row>
     <row r="709" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI709">
-        <f t="shared" si="11"/>
+        <f>SUM(AG709, AH709)</f>
         <v>0</v>
       </c>
     </row>
     <row r="710" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI710">
-        <f t="shared" si="11"/>
+        <f>SUM(AG710, AH710)</f>
         <v>0</v>
       </c>
     </row>
     <row r="711" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI711">
-        <f t="shared" si="11"/>
+        <f>SUM(AG711, AH711)</f>
         <v>0</v>
       </c>
     </row>
     <row r="712" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI712">
-        <f t="shared" si="11"/>
+        <f>SUM(AG712, AH712)</f>
         <v>0</v>
       </c>
     </row>
     <row r="713" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI713">
-        <f t="shared" si="11"/>
+        <f>SUM(AG713, AH713)</f>
         <v>0</v>
       </c>
     </row>
     <row r="714" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI714">
-        <f t="shared" si="11"/>
+        <f>SUM(AG714, AH714)</f>
         <v>0</v>
       </c>
     </row>
     <row r="715" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI715">
-        <f t="shared" si="11"/>
+        <f>SUM(AG715, AH715)</f>
         <v>0</v>
       </c>
     </row>
     <row r="716" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI716">
-        <f t="shared" si="11"/>
+        <f>SUM(AG716, AH716)</f>
         <v>0</v>
       </c>
     </row>
     <row r="717" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI717">
-        <f t="shared" si="11"/>
+        <f>SUM(AG717, AH717)</f>
         <v>0</v>
       </c>
     </row>
     <row r="718" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI718">
-        <f t="shared" si="11"/>
+        <f>SUM(AG718, AH718)</f>
         <v>0</v>
       </c>
     </row>
     <row r="719" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI719">
-        <f t="shared" si="11"/>
+        <f>SUM(AG719, AH719)</f>
         <v>0</v>
       </c>
     </row>
     <row r="720" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI720">
-        <f t="shared" si="11"/>
+        <f>SUM(AG720, AH720)</f>
         <v>0</v>
       </c>
     </row>
     <row r="721" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI721">
-        <f t="shared" si="11"/>
+        <f>SUM(AG721, AH721)</f>
         <v>0</v>
       </c>
     </row>
     <row r="722" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI722">
-        <f t="shared" si="11"/>
+        <f>SUM(AG722, AH722)</f>
         <v>0</v>
       </c>
     </row>
     <row r="723" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI723">
-        <f t="shared" si="11"/>
+        <f>SUM(AG723, AH723)</f>
         <v>0</v>
       </c>
     </row>
     <row r="724" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI724">
-        <f t="shared" si="11"/>
+        <f>SUM(AG724, AH724)</f>
         <v>0</v>
       </c>
     </row>
     <row r="725" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI725">
-        <f t="shared" si="11"/>
+        <f>SUM(AG725, AH725)</f>
         <v>0</v>
       </c>
     </row>
     <row r="726" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI726">
-        <f t="shared" si="11"/>
+        <f>SUM(AG726, AH726)</f>
         <v>0</v>
       </c>
     </row>
     <row r="727" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI727">
-        <f t="shared" si="11"/>
+        <f>SUM(AG727, AH727)</f>
         <v>0</v>
       </c>
     </row>
     <row r="728" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI728">
-        <f t="shared" si="11"/>
+        <f>SUM(AG728, AH728)</f>
         <v>0</v>
       </c>
     </row>
     <row r="729" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI729">
-        <f t="shared" si="11"/>
+        <f>SUM(AG729, AH729)</f>
         <v>0</v>
       </c>
     </row>
     <row r="730" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI730">
-        <f t="shared" si="11"/>
+        <f>SUM(AG730, AH730)</f>
         <v>0</v>
       </c>
     </row>
     <row r="731" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI731">
-        <f t="shared" si="11"/>
+        <f>SUM(AG731, AH731)</f>
         <v>0</v>
       </c>
     </row>
     <row r="732" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI732">
-        <f t="shared" si="11"/>
+        <f>SUM(AG732, AH732)</f>
         <v>0</v>
       </c>
     </row>
     <row r="733" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI733">
-        <f t="shared" si="11"/>
+        <f>SUM(AG733, AH733)</f>
         <v>0</v>
       </c>
     </row>
     <row r="734" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI734">
-        <f t="shared" si="11"/>
+        <f>SUM(AG734, AH734)</f>
         <v>0</v>
       </c>
     </row>
     <row r="735" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI735">
-        <f t="shared" si="11"/>
+        <f>SUM(AG735, AH735)</f>
         <v>0</v>
       </c>
     </row>
     <row r="736" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI736">
-        <f t="shared" si="11"/>
+        <f>SUM(AG736, AH736)</f>
         <v>0</v>
       </c>
     </row>
     <row r="737" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI737">
-        <f t="shared" si="11"/>
+        <f>SUM(AG737, AH737)</f>
         <v>0</v>
       </c>
     </row>
     <row r="738" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI738">
-        <f t="shared" si="11"/>
+        <f>SUM(AG738, AH738)</f>
         <v>0</v>
       </c>
     </row>
     <row r="739" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI739">
-        <f t="shared" si="11"/>
+        <f>SUM(AG739, AH739)</f>
         <v>0</v>
       </c>
     </row>
     <row r="740" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI740">
-        <f t="shared" si="11"/>
+        <f>SUM(AG740, AH740)</f>
         <v>0</v>
       </c>
     </row>
     <row r="741" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI741">
-        <f t="shared" si="11"/>
+        <f>SUM(AG741, AH741)</f>
         <v>0</v>
       </c>
     </row>
     <row r="742" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI742">
-        <f t="shared" si="11"/>
+        <f>SUM(AG742, AH742)</f>
         <v>0</v>
       </c>
     </row>
     <row r="743" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI743">
-        <f t="shared" si="11"/>
+        <f>SUM(AG743, AH743)</f>
         <v>0</v>
       </c>
     </row>
     <row r="744" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI744">
-        <f t="shared" si="11"/>
+        <f>SUM(AG744, AH744)</f>
         <v>0</v>
       </c>
     </row>
     <row r="745" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI745">
-        <f t="shared" si="11"/>
+        <f>SUM(AG745, AH745)</f>
         <v>0</v>
       </c>
     </row>
     <row r="746" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI746">
-        <f t="shared" si="11"/>
+        <f>SUM(AG746, AH746)</f>
         <v>0</v>
       </c>
     </row>
     <row r="747" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI747">
-        <f t="shared" si="11"/>
+        <f>SUM(AG747, AH747)</f>
         <v>0</v>
       </c>
     </row>
     <row r="748" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI748">
-        <f t="shared" si="11"/>
+        <f>SUM(AG748, AH748)</f>
         <v>0</v>
       </c>
     </row>
     <row r="749" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI749">
-        <f t="shared" si="11"/>
+        <f>SUM(AG749, AH749)</f>
         <v>0</v>
       </c>
     </row>
     <row r="750" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI750">
-        <f t="shared" si="11"/>
+        <f>SUM(AG750, AH750)</f>
         <v>0</v>
       </c>
     </row>
     <row r="751" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI751">
-        <f t="shared" si="11"/>
+        <f>SUM(AG751, AH751)</f>
         <v>0</v>
       </c>
     </row>
     <row r="752" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI752">
-        <f t="shared" si="11"/>
+        <f>SUM(AG752, AH752)</f>
         <v>0</v>
       </c>
     </row>
     <row r="753" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI753">
-        <f t="shared" si="11"/>
+        <f>SUM(AG753, AH753)</f>
         <v>0</v>
       </c>
     </row>
     <row r="754" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI754">
-        <f t="shared" si="11"/>
+        <f>SUM(AG754, AH754)</f>
         <v>0</v>
       </c>
     </row>
     <row r="755" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI755">
-        <f t="shared" si="11"/>
+        <f>SUM(AG755, AH755)</f>
         <v>0</v>
       </c>
     </row>
     <row r="756" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI756">
-        <f t="shared" si="11"/>
+        <f>SUM(AG756, AH756)</f>
         <v>0</v>
       </c>
     </row>
     <row r="757" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI757">
-        <f t="shared" si="11"/>
+        <f>SUM(AG757, AH757)</f>
         <v>0</v>
       </c>
     </row>
     <row r="758" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI758">
-        <f t="shared" si="11"/>
+        <f>SUM(AG758, AH758)</f>
         <v>0</v>
       </c>
     </row>
     <row r="759" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI759">
-        <f t="shared" si="11"/>
+        <f>SUM(AG759, AH759)</f>
         <v>0</v>
       </c>
     </row>
     <row r="760" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI760">
-        <f t="shared" si="11"/>
+        <f>SUM(AG760, AH760)</f>
         <v>0</v>
       </c>
     </row>
     <row r="761" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI761">
-        <f t="shared" si="11"/>
+        <f>SUM(AG761, AH761)</f>
         <v>0</v>
       </c>
     </row>
     <row r="762" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI762">
-        <f t="shared" si="11"/>
+        <f>SUM(AG762, AH762)</f>
         <v>0</v>
       </c>
     </row>
     <row r="763" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI763">
-        <f t="shared" si="11"/>
+        <f>SUM(AG763, AH763)</f>
         <v>0</v>
       </c>
     </row>
     <row r="764" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI764">
-        <f t="shared" si="11"/>
+        <f>SUM(AG764, AH764)</f>
         <v>0</v>
       </c>
     </row>
     <row r="765" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI765">
-        <f t="shared" si="11"/>
+        <f>SUM(AG765, AH765)</f>
         <v>0</v>
       </c>
     </row>
     <row r="766" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI766">
-        <f t="shared" si="11"/>
+        <f>SUM(AG766, AH766)</f>
         <v>0</v>
       </c>
     </row>
     <row r="767" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI767">
-        <f t="shared" si="11"/>
+        <f>SUM(AG767, AH767)</f>
         <v>0</v>
       </c>
     </row>
     <row r="768" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI768">
-        <f t="shared" si="11"/>
+        <f>SUM(AG768, AH768)</f>
         <v>0</v>
       </c>
     </row>
     <row r="769" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI769">
-        <f t="shared" si="11"/>
+        <f>SUM(AG769, AH769)</f>
         <v>0</v>
       </c>
     </row>
     <row r="770" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI770">
-        <f t="shared" ref="AI770:AI833" si="12">SUM(AG770, AH770)</f>
+        <f>SUM(AG770, AH770)</f>
         <v>0</v>
       </c>
     </row>
     <row r="771" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI771">
-        <f t="shared" si="12"/>
+        <f>SUM(AG771, AH771)</f>
         <v>0</v>
       </c>
     </row>
     <row r="772" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI772">
-        <f t="shared" si="12"/>
+        <f>SUM(AG772, AH772)</f>
         <v>0</v>
       </c>
     </row>
     <row r="773" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI773">
-        <f t="shared" si="12"/>
+        <f>SUM(AG773, AH773)</f>
         <v>0</v>
       </c>
     </row>
     <row r="774" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI774">
-        <f t="shared" si="12"/>
+        <f>SUM(AG774, AH774)</f>
         <v>0</v>
       </c>
     </row>
     <row r="775" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI775">
-        <f t="shared" si="12"/>
+        <f>SUM(AG775, AH775)</f>
         <v>0</v>
       </c>
     </row>
     <row r="776" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI776">
-        <f t="shared" si="12"/>
+        <f>SUM(AG776, AH776)</f>
         <v>0</v>
       </c>
     </row>
     <row r="777" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI777">
-        <f t="shared" si="12"/>
+        <f>SUM(AG777, AH777)</f>
         <v>0</v>
       </c>
     </row>
     <row r="778" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI778">
-        <f t="shared" si="12"/>
+        <f>SUM(AG778, AH778)</f>
         <v>0</v>
       </c>
     </row>
     <row r="779" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI779">
-        <f t="shared" si="12"/>
+        <f>SUM(AG779, AH779)</f>
         <v>0</v>
       </c>
     </row>
     <row r="780" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI780">
-        <f t="shared" si="12"/>
+        <f>SUM(AG780, AH780)</f>
         <v>0</v>
       </c>
     </row>
     <row r="781" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI781">
-        <f t="shared" si="12"/>
+        <f>SUM(AG781, AH781)</f>
         <v>0</v>
       </c>
     </row>
     <row r="782" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI782">
-        <f t="shared" si="12"/>
+        <f>SUM(AG782, AH782)</f>
         <v>0</v>
       </c>
     </row>
     <row r="783" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI783">
-        <f t="shared" si="12"/>
+        <f>SUM(AG783, AH783)</f>
         <v>0</v>
       </c>
     </row>
     <row r="784" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI784">
-        <f t="shared" si="12"/>
+        <f>SUM(AG784, AH784)</f>
         <v>0</v>
       </c>
     </row>
     <row r="785" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI785">
-        <f t="shared" si="12"/>
+        <f>SUM(AG785, AH785)</f>
         <v>0</v>
       </c>
     </row>
     <row r="786" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI786">
-        <f t="shared" si="12"/>
+        <f>SUM(AG786, AH786)</f>
         <v>0</v>
       </c>
     </row>
     <row r="787" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI787">
-        <f t="shared" si="12"/>
+        <f>SUM(AG787, AH787)</f>
         <v>0</v>
       </c>
     </row>
     <row r="788" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI788">
-        <f t="shared" si="12"/>
+        <f>SUM(AG788, AH788)</f>
         <v>0</v>
       </c>
     </row>
     <row r="789" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI789">
-        <f t="shared" si="12"/>
+        <f>SUM(AG789, AH789)</f>
         <v>0</v>
       </c>
     </row>
     <row r="790" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI790">
-        <f t="shared" si="12"/>
+        <f>SUM(AG790, AH790)</f>
         <v>0</v>
       </c>
     </row>
     <row r="791" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI791">
-        <f t="shared" si="12"/>
+        <f>SUM(AG791, AH791)</f>
         <v>0</v>
       </c>
     </row>
     <row r="792" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI792">
-        <f t="shared" si="12"/>
+        <f>SUM(AG792, AH792)</f>
         <v>0</v>
       </c>
     </row>
     <row r="793" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI793">
-        <f t="shared" si="12"/>
+        <f>SUM(AG793, AH793)</f>
         <v>0</v>
       </c>
     </row>
     <row r="794" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI794">
-        <f t="shared" si="12"/>
+        <f>SUM(AG794, AH794)</f>
         <v>0</v>
       </c>
     </row>
     <row r="795" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI795">
-        <f t="shared" si="12"/>
+        <f>SUM(AG795, AH795)</f>
         <v>0</v>
       </c>
     </row>
     <row r="796" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI796">
-        <f t="shared" si="12"/>
+        <f>SUM(AG796, AH796)</f>
         <v>0</v>
       </c>
     </row>
     <row r="797" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI797">
-        <f t="shared" si="12"/>
+        <f>SUM(AG797, AH797)</f>
         <v>0</v>
       </c>
     </row>
     <row r="798" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI798">
-        <f t="shared" si="12"/>
+        <f>SUM(AG798, AH798)</f>
         <v>0</v>
       </c>
     </row>
     <row r="799" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI799">
-        <f t="shared" si="12"/>
+        <f>SUM(AG799, AH799)</f>
         <v>0</v>
       </c>
     </row>
     <row r="800" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI800">
-        <f t="shared" si="12"/>
+        <f>SUM(AG800, AH800)</f>
         <v>0</v>
       </c>
     </row>
     <row r="801" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI801">
-        <f t="shared" si="12"/>
+        <f>SUM(AG801, AH801)</f>
         <v>0</v>
       </c>
     </row>
     <row r="802" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI802">
-        <f t="shared" si="12"/>
+        <f>SUM(AG802, AH802)</f>
         <v>0</v>
       </c>
     </row>
     <row r="803" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI803">
-        <f t="shared" si="12"/>
+        <f>SUM(AG803, AH803)</f>
         <v>0</v>
       </c>
     </row>
     <row r="804" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI804">
-        <f t="shared" si="12"/>
+        <f>SUM(AG804, AH804)</f>
         <v>0</v>
       </c>
     </row>
     <row r="805" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI805">
-        <f t="shared" si="12"/>
+        <f>SUM(AG805, AH805)</f>
         <v>0</v>
       </c>
     </row>
     <row r="806" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI806">
-        <f t="shared" si="12"/>
+        <f>SUM(AG806, AH806)</f>
         <v>0</v>
       </c>
     </row>
     <row r="807" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI807">
-        <f t="shared" si="12"/>
+        <f>SUM(AG807, AH807)</f>
         <v>0</v>
       </c>
     </row>
     <row r="808" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI808">
-        <f t="shared" si="12"/>
+        <f>SUM(AG808, AH808)</f>
         <v>0</v>
       </c>
     </row>
     <row r="809" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI809">
-        <f t="shared" si="12"/>
+        <f>SUM(AG809, AH809)</f>
         <v>0</v>
       </c>
     </row>
     <row r="810" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI810">
-        <f t="shared" si="12"/>
+        <f>SUM(AG810, AH810)</f>
         <v>0</v>
       </c>
     </row>
     <row r="811" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI811">
-        <f t="shared" si="12"/>
+        <f>SUM(AG811, AH811)</f>
         <v>0</v>
       </c>
     </row>
     <row r="812" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI812">
-        <f t="shared" si="12"/>
+        <f>SUM(AG812, AH812)</f>
         <v>0</v>
       </c>
     </row>
     <row r="813" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI813">
-        <f t="shared" si="12"/>
+        <f>SUM(AG813, AH813)</f>
         <v>0</v>
       </c>
     </row>
     <row r="814" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI814">
-        <f t="shared" si="12"/>
+        <f>SUM(AG814, AH814)</f>
         <v>0</v>
       </c>
     </row>
     <row r="815" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI815">
-        <f t="shared" si="12"/>
+        <f>SUM(AG815, AH815)</f>
         <v>0</v>
       </c>
     </row>
     <row r="816" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI816">
-        <f t="shared" si="12"/>
+        <f>SUM(AG816, AH816)</f>
         <v>0</v>
       </c>
     </row>
     <row r="817" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI817">
-        <f t="shared" si="12"/>
+        <f>SUM(AG817, AH817)</f>
         <v>0</v>
       </c>
     </row>
     <row r="818" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI818">
-        <f t="shared" si="12"/>
+        <f>SUM(AG818, AH818)</f>
         <v>0</v>
       </c>
     </row>
     <row r="819" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI819">
-        <f t="shared" si="12"/>
+        <f>SUM(AG819, AH819)</f>
         <v>0</v>
       </c>
     </row>
     <row r="820" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI820">
-        <f t="shared" si="12"/>
+        <f>SUM(AG820, AH820)</f>
         <v>0</v>
       </c>
     </row>
     <row r="821" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI821">
-        <f t="shared" si="12"/>
+        <f>SUM(AG821, AH821)</f>
         <v>0</v>
       </c>
     </row>
     <row r="822" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI822">
-        <f t="shared" si="12"/>
+        <f>SUM(AG822, AH822)</f>
         <v>0</v>
       </c>
     </row>
     <row r="823" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI823">
-        <f t="shared" si="12"/>
+        <f>SUM(AG823, AH823)</f>
         <v>0</v>
       </c>
     </row>
     <row r="824" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI824">
-        <f t="shared" si="12"/>
+        <f>SUM(AG824, AH824)</f>
         <v>0</v>
       </c>
     </row>
     <row r="825" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI825">
-        <f t="shared" si="12"/>
+        <f>SUM(AG825, AH825)</f>
         <v>0</v>
       </c>
     </row>
     <row r="826" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI826">
-        <f t="shared" si="12"/>
+        <f>SUM(AG826, AH826)</f>
         <v>0</v>
       </c>
     </row>
     <row r="827" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI827">
-        <f t="shared" si="12"/>
+        <f>SUM(AG827, AH827)</f>
         <v>0</v>
       </c>
     </row>
     <row r="828" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI828">
-        <f t="shared" si="12"/>
+        <f>SUM(AG828, AH828)</f>
         <v>0</v>
       </c>
     </row>
     <row r="829" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI829">
-        <f t="shared" si="12"/>
+        <f>SUM(AG829, AH829)</f>
         <v>0</v>
       </c>
     </row>
     <row r="830" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI830">
-        <f t="shared" si="12"/>
+        <f>SUM(AG830, AH830)</f>
         <v>0</v>
       </c>
     </row>
     <row r="831" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI831">
-        <f t="shared" si="12"/>
+        <f>SUM(AG831, AH831)</f>
         <v>0</v>
       </c>
     </row>
     <row r="832" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI832">
-        <f t="shared" si="12"/>
+        <f>SUM(AG832, AH832)</f>
         <v>0</v>
       </c>
     </row>
     <row r="833" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI833">
-        <f t="shared" si="12"/>
+        <f>SUM(AG833, AH833)</f>
         <v>0</v>
       </c>
     </row>
     <row r="834" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI834">
-        <f t="shared" ref="AI834:AI897" si="13">SUM(AG834, AH834)</f>
+        <f>SUM(AG834, AH834)</f>
         <v>0</v>
       </c>
     </row>
     <row r="835" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI835">
-        <f t="shared" si="13"/>
+        <f>SUM(AG835, AH835)</f>
         <v>0</v>
       </c>
     </row>
     <row r="836" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI836">
-        <f t="shared" si="13"/>
+        <f>SUM(AG836, AH836)</f>
         <v>0</v>
       </c>
     </row>
     <row r="837" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI837">
-        <f t="shared" si="13"/>
+        <f>SUM(AG837, AH837)</f>
         <v>0</v>
       </c>
     </row>
     <row r="838" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI838">
-        <f t="shared" si="13"/>
+        <f>SUM(AG838, AH838)</f>
         <v>0</v>
       </c>
     </row>
     <row r="839" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI839">
-        <f t="shared" si="13"/>
+        <f>SUM(AG839, AH839)</f>
         <v>0</v>
       </c>
     </row>
     <row r="840" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI840">
-        <f t="shared" si="13"/>
+        <f>SUM(AG840, AH840)</f>
         <v>0</v>
       </c>
     </row>
     <row r="841" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI841">
-        <f t="shared" si="13"/>
+        <f>SUM(AG841, AH841)</f>
         <v>0</v>
       </c>
     </row>
     <row r="842" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI842">
-        <f t="shared" si="13"/>
+        <f>SUM(AG842, AH842)</f>
         <v>0</v>
       </c>
     </row>
     <row r="843" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI843">
-        <f t="shared" si="13"/>
+        <f>SUM(AG843, AH843)</f>
         <v>0</v>
       </c>
     </row>
     <row r="844" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI844">
-        <f t="shared" si="13"/>
+        <f>SUM(AG844, AH844)</f>
         <v>0</v>
       </c>
     </row>
     <row r="845" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI845">
-        <f t="shared" si="13"/>
+        <f>SUM(AG845, AH845)</f>
         <v>0</v>
       </c>
     </row>
     <row r="846" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI846">
-        <f t="shared" si="13"/>
+        <f>SUM(AG846, AH846)</f>
         <v>0</v>
       </c>
     </row>
     <row r="847" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI847">
-        <f t="shared" si="13"/>
+        <f>SUM(AG847, AH847)</f>
         <v>0</v>
       </c>
     </row>
     <row r="848" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI848">
-        <f t="shared" si="13"/>
+        <f>SUM(AG848, AH848)</f>
         <v>0</v>
       </c>
     </row>
     <row r="849" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI849">
-        <f t="shared" si="13"/>
+        <f>SUM(AG849, AH849)</f>
         <v>0</v>
       </c>
     </row>
     <row r="850" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI850">
-        <f t="shared" si="13"/>
+        <f>SUM(AG850, AH850)</f>
         <v>0</v>
       </c>
     </row>
     <row r="851" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI851">
-        <f t="shared" si="13"/>
+        <f>SUM(AG851, AH851)</f>
         <v>0</v>
       </c>
     </row>
     <row r="852" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI852">
-        <f t="shared" si="13"/>
+        <f>SUM(AG852, AH852)</f>
         <v>0</v>
       </c>
     </row>
     <row r="853" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI853">
-        <f t="shared" si="13"/>
+        <f>SUM(AG853, AH853)</f>
         <v>0</v>
       </c>
     </row>
     <row r="854" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI854">
-        <f t="shared" si="13"/>
+        <f>SUM(AG854, AH854)</f>
         <v>0</v>
       </c>
     </row>
     <row r="855" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI855">
-        <f t="shared" si="13"/>
+        <f>SUM(AG855, AH855)</f>
         <v>0</v>
       </c>
     </row>
     <row r="856" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI856">
-        <f t="shared" si="13"/>
+        <f>SUM(AG856, AH856)</f>
         <v>0</v>
       </c>
     </row>
     <row r="857" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI857">
-        <f t="shared" si="13"/>
+        <f>SUM(AG857, AH857)</f>
         <v>0</v>
       </c>
     </row>
     <row r="858" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI858">
-        <f t="shared" si="13"/>
+        <f>SUM(AG858, AH858)</f>
         <v>0</v>
       </c>
     </row>
     <row r="859" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI859">
-        <f t="shared" si="13"/>
+        <f>SUM(AG859, AH859)</f>
         <v>0</v>
       </c>
     </row>
     <row r="860" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI860">
-        <f t="shared" si="13"/>
+        <f>SUM(AG860, AH860)</f>
         <v>0</v>
       </c>
     </row>
     <row r="861" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI861">
-        <f t="shared" si="13"/>
+        <f>SUM(AG861, AH861)</f>
         <v>0</v>
       </c>
     </row>
     <row r="862" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI862">
-        <f t="shared" si="13"/>
+        <f>SUM(AG862, AH862)</f>
         <v>0</v>
       </c>
     </row>
     <row r="863" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI863">
-        <f t="shared" si="13"/>
+        <f>SUM(AG863, AH863)</f>
         <v>0</v>
       </c>
     </row>
     <row r="864" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI864">
-        <f t="shared" si="13"/>
+        <f>SUM(AG864, AH864)</f>
         <v>0</v>
       </c>
     </row>
     <row r="865" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI865">
-        <f t="shared" si="13"/>
+        <f>SUM(AG865, AH865)</f>
         <v>0</v>
       </c>
     </row>
     <row r="866" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI866">
-        <f t="shared" si="13"/>
+        <f>SUM(AG866, AH866)</f>
         <v>0</v>
       </c>
     </row>
     <row r="867" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI867">
-        <f t="shared" si="13"/>
+        <f>SUM(AG867, AH867)</f>
         <v>0</v>
       </c>
     </row>
     <row r="868" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI868">
-        <f t="shared" si="13"/>
+        <f>SUM(AG868, AH868)</f>
         <v>0</v>
       </c>
     </row>
     <row r="869" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI869">
-        <f t="shared" si="13"/>
+        <f>SUM(AG869, AH869)</f>
         <v>0</v>
       </c>
     </row>
     <row r="870" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI870">
-        <f t="shared" si="13"/>
+        <f>SUM(AG870, AH870)</f>
         <v>0</v>
       </c>
     </row>
     <row r="871" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI871">
-        <f t="shared" si="13"/>
+        <f>SUM(AG871, AH871)</f>
         <v>0</v>
       </c>
     </row>
     <row r="872" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI872">
-        <f t="shared" si="13"/>
+        <f>SUM(AG872, AH872)</f>
         <v>0</v>
       </c>
     </row>
     <row r="873" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI873">
-        <f t="shared" si="13"/>
+        <f>SUM(AG873, AH873)</f>
         <v>0</v>
       </c>
     </row>
     <row r="874" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI874">
-        <f t="shared" si="13"/>
+        <f>SUM(AG874, AH874)</f>
         <v>0</v>
       </c>
     </row>
     <row r="875" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI875">
-        <f t="shared" si="13"/>
+        <f>SUM(AG875, AH875)</f>
         <v>0</v>
       </c>
     </row>
     <row r="876" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI876">
-        <f t="shared" si="13"/>
+        <f>SUM(AG876, AH876)</f>
         <v>0</v>
       </c>
     </row>
     <row r="877" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI877">
-        <f t="shared" si="13"/>
+        <f>SUM(AG877, AH877)</f>
         <v>0</v>
       </c>
     </row>
     <row r="878" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI878">
-        <f t="shared" si="13"/>
+        <f>SUM(AG878, AH878)</f>
         <v>0</v>
       </c>
     </row>
     <row r="879" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI879">
-        <f t="shared" si="13"/>
+        <f>SUM(AG879, AH879)</f>
         <v>0</v>
       </c>
     </row>
     <row r="880" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI880">
-        <f t="shared" si="13"/>
+        <f>SUM(AG880, AH880)</f>
         <v>0</v>
       </c>
     </row>
     <row r="881" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI881">
-        <f t="shared" si="13"/>
+        <f>SUM(AG881, AH881)</f>
         <v>0</v>
       </c>
     </row>
     <row r="882" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI882">
-        <f t="shared" si="13"/>
+        <f>SUM(AG882, AH882)</f>
         <v>0</v>
       </c>
     </row>
     <row r="883" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI883">
-        <f t="shared" si="13"/>
+        <f>SUM(AG883, AH883)</f>
         <v>0</v>
       </c>
     </row>
     <row r="884" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI884">
-        <f t="shared" si="13"/>
+        <f>SUM(AG884, AH884)</f>
         <v>0</v>
       </c>
     </row>
     <row r="885" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI885">
-        <f t="shared" si="13"/>
+        <f>SUM(AG885, AH885)</f>
         <v>0</v>
       </c>
     </row>
     <row r="886" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI886">
-        <f t="shared" si="13"/>
+        <f>SUM(AG886, AH886)</f>
         <v>0</v>
       </c>
     </row>
     <row r="887" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI887">
-        <f t="shared" si="13"/>
+        <f>SUM(AG887, AH887)</f>
         <v>0</v>
       </c>
     </row>
     <row r="888" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI888">
-        <f t="shared" si="13"/>
+        <f>SUM(AG888, AH888)</f>
         <v>0</v>
       </c>
     </row>
     <row r="889" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI889">
-        <f t="shared" si="13"/>
+        <f>SUM(AG889, AH889)</f>
         <v>0</v>
       </c>
     </row>
     <row r="890" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI890">
-        <f t="shared" si="13"/>
+        <f>SUM(AG890, AH890)</f>
         <v>0</v>
       </c>
     </row>
     <row r="891" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI891">
-        <f t="shared" si="13"/>
+        <f>SUM(AG891, AH891)</f>
         <v>0</v>
       </c>
     </row>
     <row r="892" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI892">
-        <f t="shared" si="13"/>
+        <f>SUM(AG892, AH892)</f>
         <v>0</v>
       </c>
     </row>
     <row r="893" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI893">
-        <f t="shared" si="13"/>
+        <f>SUM(AG893, AH893)</f>
         <v>0</v>
       </c>
     </row>
     <row r="894" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI894">
-        <f t="shared" si="13"/>
+        <f>SUM(AG894, AH894)</f>
         <v>0</v>
       </c>
     </row>
     <row r="895" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI895">
-        <f t="shared" si="13"/>
+        <f>SUM(AG895, AH895)</f>
         <v>0</v>
       </c>
     </row>
     <row r="896" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI896">
-        <f t="shared" si="13"/>
+        <f>SUM(AG896, AH896)</f>
         <v>0</v>
       </c>
     </row>
     <row r="897" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI897">
-        <f t="shared" si="13"/>
+        <f>SUM(AG897, AH897)</f>
         <v>0</v>
       </c>
     </row>
     <row r="898" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI898">
-        <f t="shared" ref="AI898:AI961" si="14">SUM(AG898, AH898)</f>
+        <f>SUM(AG898, AH898)</f>
         <v>0</v>
       </c>
     </row>
     <row r="899" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI899">
-        <f t="shared" si="14"/>
+        <f>SUM(AG899, AH899)</f>
         <v>0</v>
       </c>
     </row>
     <row r="900" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI900">
-        <f t="shared" si="14"/>
+        <f>SUM(AG900, AH900)</f>
         <v>0</v>
       </c>
     </row>
     <row r="901" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI901">
-        <f t="shared" si="14"/>
+        <f>SUM(AG901, AH901)</f>
         <v>0</v>
       </c>
     </row>
     <row r="902" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI902">
-        <f t="shared" si="14"/>
+        <f>SUM(AG902, AH902)</f>
         <v>0</v>
       </c>
     </row>
     <row r="903" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI903">
-        <f t="shared" si="14"/>
+        <f>SUM(AG903, AH903)</f>
         <v>0</v>
       </c>
     </row>
     <row r="904" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI904">
-        <f t="shared" si="14"/>
+        <f>SUM(AG904, AH904)</f>
         <v>0</v>
       </c>
     </row>
     <row r="905" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI905">
-        <f t="shared" si="14"/>
+        <f>SUM(AG905, AH905)</f>
         <v>0</v>
       </c>
     </row>
     <row r="906" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI906">
-        <f t="shared" si="14"/>
+        <f>SUM(AG906, AH906)</f>
         <v>0</v>
       </c>
     </row>
     <row r="907" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI907">
-        <f t="shared" si="14"/>
+        <f>SUM(AG907, AH907)</f>
         <v>0</v>
       </c>
     </row>
     <row r="908" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI908">
-        <f t="shared" si="14"/>
+        <f>SUM(AG908, AH908)</f>
         <v>0</v>
       </c>
     </row>
     <row r="909" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI909">
-        <f t="shared" si="14"/>
+        <f>SUM(AG909, AH909)</f>
         <v>0</v>
       </c>
     </row>
     <row r="910" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI910">
-        <f t="shared" si="14"/>
+        <f>SUM(AG910, AH910)</f>
         <v>0</v>
       </c>
     </row>
     <row r="911" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI911">
-        <f t="shared" si="14"/>
+        <f>SUM(AG911, AH911)</f>
         <v>0</v>
       </c>
     </row>
     <row r="912" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI912">
-        <f t="shared" si="14"/>
+        <f>SUM(AG912, AH912)</f>
         <v>0</v>
       </c>
     </row>
     <row r="913" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI913">
-        <f t="shared" si="14"/>
+        <f>SUM(AG913, AH913)</f>
         <v>0</v>
       </c>
     </row>
     <row r="914" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI914">
-        <f t="shared" si="14"/>
+        <f>SUM(AG914, AH914)</f>
         <v>0</v>
       </c>
     </row>
     <row r="915" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI915">
-        <f t="shared" si="14"/>
+        <f>SUM(AG915, AH915)</f>
         <v>0</v>
       </c>
     </row>
     <row r="916" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI916">
-        <f t="shared" si="14"/>
+        <f>SUM(AG916, AH916)</f>
         <v>0</v>
       </c>
     </row>
     <row r="917" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI917">
-        <f t="shared" si="14"/>
+        <f>SUM(AG917, AH917)</f>
         <v>0</v>
       </c>
     </row>
     <row r="918" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI918">
-        <f t="shared" si="14"/>
+        <f>SUM(AG918, AH918)</f>
         <v>0</v>
       </c>
     </row>
     <row r="919" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI919">
-        <f t="shared" si="14"/>
+        <f>SUM(AG919, AH919)</f>
         <v>0</v>
       </c>
     </row>
     <row r="920" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI920">
-        <f t="shared" si="14"/>
+        <f>SUM(AG920, AH920)</f>
         <v>0</v>
       </c>
     </row>
     <row r="921" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI921">
-        <f t="shared" si="14"/>
+        <f>SUM(AG921, AH921)</f>
         <v>0</v>
       </c>
     </row>
     <row r="922" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI922">
-        <f t="shared" si="14"/>
+        <f>SUM(AG922, AH922)</f>
         <v>0</v>
       </c>
     </row>
     <row r="923" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI923">
-        <f t="shared" si="14"/>
+        <f>SUM(AG923, AH923)</f>
         <v>0</v>
       </c>
     </row>
     <row r="924" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI924">
-        <f t="shared" si="14"/>
+        <f>SUM(AG924, AH924)</f>
         <v>0</v>
       </c>
     </row>
     <row r="925" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI925">
-        <f t="shared" si="14"/>
+        <f>SUM(AG925, AH925)</f>
         <v>0</v>
       </c>
     </row>
     <row r="926" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI926">
-        <f t="shared" si="14"/>
+        <f>SUM(AG926, AH926)</f>
         <v>0</v>
       </c>
     </row>
     <row r="927" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI927">
-        <f t="shared" si="14"/>
+        <f>SUM(AG927, AH927)</f>
         <v>0</v>
       </c>
     </row>
     <row r="928" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI928">
-        <f t="shared" si="14"/>
+        <f>SUM(AG928, AH928)</f>
         <v>0</v>
       </c>
     </row>
     <row r="929" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI929">
-        <f t="shared" si="14"/>
+        <f>SUM(AG929, AH929)</f>
         <v>0</v>
       </c>
     </row>
     <row r="930" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI930">
-        <f t="shared" si="14"/>
+        <f>SUM(AG930, AH930)</f>
         <v>0</v>
       </c>
     </row>
     <row r="931" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI931">
-        <f t="shared" si="14"/>
+        <f>SUM(AG931, AH931)</f>
         <v>0</v>
       </c>
     </row>
     <row r="932" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI932">
-        <f t="shared" si="14"/>
+        <f>SUM(AG932, AH932)</f>
         <v>0</v>
       </c>
     </row>
     <row r="933" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI933">
-        <f t="shared" si="14"/>
+        <f>SUM(AG933, AH933)</f>
         <v>0</v>
       </c>
     </row>
     <row r="934" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI934">
-        <f t="shared" si="14"/>
+        <f>SUM(AG934, AH934)</f>
         <v>0</v>
       </c>
     </row>
     <row r="935" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI935">
-        <f t="shared" si="14"/>
+        <f>SUM(AG935, AH935)</f>
         <v>0</v>
       </c>
     </row>
     <row r="936" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI936">
-        <f t="shared" si="14"/>
+        <f>SUM(AG936, AH936)</f>
         <v>0</v>
       </c>
     </row>
     <row r="937" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI937">
-        <f t="shared" si="14"/>
+        <f>SUM(AG937, AH937)</f>
         <v>0</v>
       </c>
     </row>
     <row r="938" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI938">
-        <f t="shared" si="14"/>
+        <f>SUM(AG938, AH938)</f>
         <v>0</v>
       </c>
     </row>
     <row r="939" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI939">
-        <f t="shared" si="14"/>
+        <f>SUM(AG939, AH939)</f>
         <v>0</v>
       </c>
     </row>
     <row r="940" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI940">
-        <f t="shared" si="14"/>
+        <f>SUM(AG940, AH940)</f>
         <v>0</v>
       </c>
     </row>
     <row r="941" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI941">
-        <f t="shared" si="14"/>
+        <f>SUM(AG941, AH941)</f>
         <v>0</v>
       </c>
     </row>
     <row r="942" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI942">
-        <f t="shared" si="14"/>
+        <f>SUM(AG942, AH942)</f>
         <v>0</v>
       </c>
     </row>
     <row r="943" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI943">
-        <f t="shared" si="14"/>
+        <f>SUM(AG943, AH943)</f>
         <v>0</v>
       </c>
     </row>
     <row r="944" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI944">
-        <f t="shared" si="14"/>
+        <f>SUM(AG944, AH944)</f>
         <v>0</v>
       </c>
     </row>
     <row r="945" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI945">
-        <f t="shared" si="14"/>
+        <f>SUM(AG945, AH945)</f>
         <v>0</v>
       </c>
     </row>
     <row r="946" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI946">
-        <f t="shared" si="14"/>
+        <f>SUM(AG946, AH946)</f>
         <v>0</v>
       </c>
     </row>
     <row r="947" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI947">
-        <f t="shared" si="14"/>
+        <f>SUM(AG947, AH947)</f>
         <v>0</v>
       </c>
     </row>
     <row r="948" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI948">
-        <f t="shared" si="14"/>
+        <f>SUM(AG948, AH948)</f>
         <v>0</v>
       </c>
     </row>
     <row r="949" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI949">
-        <f t="shared" si="14"/>
+        <f>SUM(AG949, AH949)</f>
         <v>0</v>
       </c>
     </row>
     <row r="950" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI950">
-        <f t="shared" si="14"/>
+        <f>SUM(AG950, AH950)</f>
         <v>0</v>
       </c>
     </row>
     <row r="951" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI951">
-        <f t="shared" si="14"/>
+        <f>SUM(AG951, AH951)</f>
         <v>0</v>
       </c>
     </row>
     <row r="952" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI952">
-        <f t="shared" si="14"/>
+        <f>SUM(AG952, AH952)</f>
         <v>0</v>
       </c>
     </row>
     <row r="953" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI953">
-        <f t="shared" si="14"/>
+        <f>SUM(AG953, AH953)</f>
         <v>0</v>
       </c>
     </row>
     <row r="954" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI954">
-        <f t="shared" si="14"/>
+        <f>SUM(AG954, AH954)</f>
         <v>0</v>
       </c>
     </row>
     <row r="955" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI955">
-        <f t="shared" si="14"/>
+        <f>SUM(AG955, AH955)</f>
         <v>0</v>
       </c>
     </row>
     <row r="956" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI956">
-        <f t="shared" si="14"/>
+        <f>SUM(AG956, AH956)</f>
         <v>0</v>
       </c>
     </row>
     <row r="957" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI957">
-        <f t="shared" si="14"/>
+        <f>SUM(AG957, AH957)</f>
         <v>0</v>
       </c>
     </row>
     <row r="958" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI958">
-        <f t="shared" si="14"/>
+        <f>SUM(AG958, AH958)</f>
         <v>0</v>
       </c>
     </row>
     <row r="959" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI959">
-        <f t="shared" si="14"/>
+        <f>SUM(AG959, AH959)</f>
         <v>0</v>
       </c>
     </row>
     <row r="960" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI960">
-        <f t="shared" si="14"/>
+        <f>SUM(AG960, AH960)</f>
         <v>0</v>
       </c>
     </row>
     <row r="961" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI961">
-        <f t="shared" si="14"/>
+        <f>SUM(AG961, AH961)</f>
         <v>0</v>
       </c>
     </row>
     <row r="962" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI962">
-        <f t="shared" ref="AI962:AI1025" si="15">SUM(AG962, AH962)</f>
+        <f>SUM(AG962, AH962)</f>
         <v>0</v>
       </c>
     </row>
     <row r="963" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI963">
-        <f t="shared" si="15"/>
+        <f>SUM(AG963, AH963)</f>
         <v>0</v>
       </c>
     </row>
     <row r="964" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI964">
-        <f t="shared" si="15"/>
+        <f>SUM(AG964, AH964)</f>
         <v>0</v>
       </c>
     </row>
     <row r="965" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI965">
-        <f t="shared" si="15"/>
+        <f>SUM(AG965, AH965)</f>
         <v>0</v>
       </c>
     </row>
     <row r="966" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI966">
-        <f t="shared" si="15"/>
+        <f>SUM(AG966, AH966)</f>
         <v>0</v>
       </c>
     </row>
     <row r="967" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI967">
-        <f t="shared" si="15"/>
+        <f>SUM(AG967, AH967)</f>
         <v>0</v>
       </c>
     </row>
     <row r="968" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI968">
-        <f t="shared" si="15"/>
+        <f>SUM(AG968, AH968)</f>
         <v>0</v>
       </c>
     </row>
     <row r="969" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI969">
-        <f t="shared" si="15"/>
+        <f>SUM(AG969, AH969)</f>
         <v>0</v>
       </c>
     </row>
     <row r="970" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI970">
-        <f t="shared" si="15"/>
+        <f>SUM(AG970, AH970)</f>
         <v>0</v>
       </c>
     </row>
     <row r="971" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI971">
-        <f t="shared" si="15"/>
+        <f>SUM(AG971, AH971)</f>
         <v>0</v>
       </c>
     </row>
     <row r="972" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI972">
-        <f t="shared" si="15"/>
+        <f>SUM(AG972, AH972)</f>
         <v>0</v>
       </c>
     </row>
     <row r="973" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI973">
-        <f t="shared" si="15"/>
+        <f>SUM(AG973, AH973)</f>
         <v>0</v>
       </c>
     </row>
     <row r="974" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI974">
-        <f t="shared" si="15"/>
+        <f>SUM(AG974, AH974)</f>
         <v>0</v>
       </c>
     </row>
     <row r="975" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI975">
-        <f t="shared" si="15"/>
+        <f>SUM(AG975, AH975)</f>
         <v>0</v>
       </c>
     </row>
     <row r="976" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI976">
-        <f t="shared" si="15"/>
+        <f>SUM(AG976, AH976)</f>
         <v>0</v>
       </c>
     </row>
     <row r="977" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI977">
-        <f t="shared" si="15"/>
+        <f>SUM(AG977, AH977)</f>
         <v>0</v>
       </c>
     </row>
     <row r="978" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI978">
-        <f t="shared" si="15"/>
+        <f>SUM(AG978, AH978)</f>
         <v>0</v>
       </c>
     </row>
     <row r="979" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI979">
-        <f t="shared" si="15"/>
+        <f>SUM(AG979, AH979)</f>
         <v>0</v>
       </c>
     </row>
     <row r="980" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI980">
-        <f t="shared" si="15"/>
+        <f>SUM(AG980, AH980)</f>
         <v>0</v>
       </c>
     </row>
     <row r="981" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI981">
-        <f t="shared" si="15"/>
+        <f>SUM(AG981, AH981)</f>
         <v>0</v>
       </c>
     </row>
     <row r="982" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI982">
-        <f t="shared" si="15"/>
+        <f>SUM(AG982, AH982)</f>
         <v>0</v>
       </c>
     </row>
     <row r="983" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI983">
-        <f t="shared" si="15"/>
+        <f>SUM(AG983, AH983)</f>
         <v>0</v>
       </c>
     </row>
     <row r="984" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI984">
-        <f t="shared" si="15"/>
+        <f>SUM(AG984, AH984)</f>
         <v>0</v>
       </c>
     </row>
     <row r="985" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI985">
-        <f t="shared" si="15"/>
+        <f>SUM(AG985, AH985)</f>
         <v>0</v>
       </c>
     </row>
     <row r="986" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI986">
-        <f t="shared" si="15"/>
+        <f>SUM(AG986, AH986)</f>
         <v>0</v>
       </c>
     </row>
     <row r="987" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI987">
-        <f t="shared" si="15"/>
+        <f>SUM(AG987, AH987)</f>
         <v>0</v>
       </c>
     </row>
     <row r="988" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI988">
-        <f t="shared" si="15"/>
+        <f>SUM(AG988, AH988)</f>
         <v>0</v>
       </c>
     </row>
     <row r="989" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI989">
-        <f t="shared" si="15"/>
+        <f>SUM(AG989, AH989)</f>
         <v>0</v>
       </c>
     </row>
     <row r="990" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI990">
-        <f t="shared" si="15"/>
+        <f>SUM(AG990, AH990)</f>
         <v>0</v>
       </c>
     </row>
     <row r="991" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI991">
-        <f t="shared" si="15"/>
+        <f>SUM(AG991, AH991)</f>
         <v>0</v>
       </c>
     </row>
     <row r="992" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI992">
-        <f t="shared" si="15"/>
+        <f>SUM(AG992, AH992)</f>
         <v>0</v>
       </c>
     </row>
     <row r="993" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI993">
-        <f t="shared" si="15"/>
+        <f>SUM(AG993, AH993)</f>
         <v>0</v>
       </c>
     </row>
     <row r="994" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI994">
-        <f t="shared" si="15"/>
+        <f>SUM(AG994, AH994)</f>
         <v>0</v>
       </c>
     </row>
     <row r="995" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI995">
-        <f t="shared" si="15"/>
+        <f>SUM(AG995, AH995)</f>
         <v>0</v>
       </c>
     </row>
     <row r="996" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI996">
-        <f t="shared" si="15"/>
+        <f>SUM(AG996, AH996)</f>
         <v>0</v>
       </c>
     </row>
     <row r="997" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI997">
-        <f t="shared" si="15"/>
+        <f>SUM(AG997, AH997)</f>
         <v>0</v>
       </c>
     </row>
     <row r="998" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI998">
-        <f t="shared" si="15"/>
+        <f>SUM(AG998, AH998)</f>
         <v>0</v>
       </c>
     </row>
     <row r="999" spans="35:35" x14ac:dyDescent="0.25">
       <c r="AI999">
-        <f t="shared" si="15"/>
+        <f>SUM(AG999, AH999)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AI9"/>
   <conditionalFormatting sqref="G2:G10000">
     <cfRule type="dataBar" priority="1">
       <dataBar>
@@ -7679,7 +7956,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DA7ABA51-AAAA-BBBB-0001-000000000001}</x14:id>
+          <x14:id>{DA7ABA51-AAAA-BBBB-0002-000000000001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7687,8 +7964,8 @@
   <conditionalFormatting sqref="I2:I10000">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFA91B0D"/>
       </colorScale>
@@ -7697,19 +7974,27 @@
   <conditionalFormatting sqref="M2:M10000">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFFF6C74"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O10000">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="TRUE">
+  <conditionalFormatting sqref="N2:N10000">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",N2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",N2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O10000">
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",O2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",O2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P10000">
@@ -7721,7 +8006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DA7ABA51-AAAA-BBBB-0001-000000000002}</x14:id>
+          <x14:id>{DA7ABA51-AAAA-BBBB-0002-000000000002}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7732,21 +8017,21 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D4" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D6" r:id="rId5"/>
+    <hyperlink ref="D7" r:id="rId6"/>
+    <hyperlink ref="D8" r:id="rId7"/>
+    <hyperlink ref="D9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0001-000000000001}">
+          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0002-000000000001}">
             <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7759,7 +8044,7 @@
           <xm:sqref>G2:G10000</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0001-000000000002}">
+          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0002-000000000002}">
             <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -7774,4 +8059,14 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>